--- a/docs/cikti_taslagi_dolu.xlsx
+++ b/docs/cikti_taslagi_dolu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muhammed.bulut\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD33D07-5CA7-49F8-9DCE-89CDABA150FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2600EB8C-3770-49B8-AD62-ABF4530971C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
     <definedName name="ilanNo">#REF!</definedName>
     <definedName name="MTarihi">#REF!</definedName>
     <definedName name="Muhammed_Taha_Kayaoğlu">[1]AG!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Karar Tutanağı'!$B$2:$L$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Karar Tutanağı'!$B$2:$L$31</definedName>
     <definedName name="YIL">[2]Adaylar!$CE$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
   <si>
     <t xml:space="preserve">AD SOYAD </t>
   </si>
@@ -128,58 +128,61 @@
     <t>Toplam</t>
   </si>
   <si>
+    <t>4a</t>
+  </si>
+  <si>
+    <t>TÜBİTAK</t>
+  </si>
+  <si>
+    <t>Araştırmacı</t>
+  </si>
+  <si>
+    <t>E-Devlet</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
     <t>4b</t>
   </si>
   <si>
-    <t>4a</t>
+    <t>ASELSAN</t>
+  </si>
+  <si>
+    <t>Çalışan</t>
   </si>
   <si>
     <t>4c</t>
   </si>
   <si>
-    <t>TÜBİTAK</t>
-  </si>
-  <si>
-    <t>Araştırmacı</t>
-  </si>
-  <si>
-    <t>ASELSAN</t>
-  </si>
-  <si>
     <t>TUSAŞ</t>
   </si>
   <si>
-    <t>Çalışan</t>
-  </si>
-  <si>
     <t>Müdür</t>
   </si>
   <si>
-    <t>E-Devlet</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
     <t>H</t>
   </si>
   <si>
+    <t>Lisans</t>
+  </si>
+  <si>
+    <t>Yıldız Teknik Üniversitesi</t>
+  </si>
+  <si>
+    <t>Bilgisayar Mühendisliği</t>
+  </si>
+  <si>
+    <t>Matematik Mühendisliği</t>
+  </si>
+  <si>
+    <t>Tezli Yüksek Lisans</t>
+  </si>
+  <si>
     <t>Yüksek Lisans</t>
   </si>
   <si>
-    <t>Yıldız Teknik Üniversitesi</t>
-  </si>
-  <si>
-    <t>Bilgisayar Mühendisliği</t>
-  </si>
-  <si>
-    <t>Lisans</t>
-  </si>
-  <si>
     <t>Doktora</t>
-  </si>
-  <si>
-    <t>Kadrolu</t>
   </si>
 </sst>
 </file>
@@ -334,7 +337,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -407,12 +410,87 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -423,9 +501,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -450,14 +525,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -481,9 +548,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="14" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -519,93 +583,999 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Virgül 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="57">
+  <dxfs count="144">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1513,7 +2483,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AM24"/>
+  <dimension ref="B1:AM31"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.44140625" customWidth="1"/>
@@ -1533,31 +2503,31 @@
   <sheetData>
     <row r="1" spans="2:39" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:39" s="1" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="F2" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="53" t="s">
+      <c r="H2" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="55"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="46"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
@@ -1572,19 +2542,17 @@
       <c r="Z2" s="2"/>
     </row>
     <row r="3" spans="2:39" s="1" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="56" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="58"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="49"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
@@ -1599,19 +2567,19 @@
       <c r="Z3" s="2"/>
     </row>
     <row r="4" spans="2:39" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
@@ -1629,25 +2597,25 @@
       <c r="AC4" s="2"/>
     </row>
     <row r="5" spans="2:39" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="20"/>
-      <c r="C5" s="44" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44" t="s">
+      <c r="D5" s="51"/>
+      <c r="E5" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44" t="s">
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44" t="s">
+      <c r="J5" s="51"/>
+      <c r="K5" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="L5" s="44"/>
+      <c r="L5" s="51"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
@@ -1665,935 +2633,1608 @@
       <c r="AC5" s="2"/>
     </row>
     <row r="6" spans="2:39" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="45" t="s">
+      <c r="B6" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="45"/>
-      <c r="E6" s="46" t="s">
+      <c r="D6" s="42"/>
+      <c r="E6" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="60">
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="52">
         <v>43881</v>
       </c>
-      <c r="J6" s="60"/>
-      <c r="K6" s="45" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" s="45"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16"/>
-      <c r="V6" s="16"/>
-      <c r="W6" s="16"/>
-      <c r="X6" s="16"/>
-      <c r="Y6" s="16"/>
-      <c r="Z6" s="16"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="42"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="13"/>
       <c r="AA6" s="2"/>
       <c r="AB6" s="2"/>
       <c r="AC6" s="2"/>
     </row>
     <row r="7" spans="2:39" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="C7" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="45"/>
-      <c r="E7" s="46" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="60">
+      <c r="D7" s="42"/>
+      <c r="E7" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="52">
         <v>44247</v>
       </c>
-      <c r="J7" s="60"/>
-      <c r="K7" s="45" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="45"/>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
-      <c r="S7" s="16"/>
-      <c r="T7" s="16"/>
-      <c r="U7" s="16"/>
-      <c r="V7" s="16"/>
-      <c r="W7" s="16"/>
-      <c r="X7" s="16"/>
-      <c r="Y7" s="16"/>
-      <c r="Z7" s="16"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" s="42"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="13"/>
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="13"/>
       <c r="AA7" s="2"/>
       <c r="AB7" s="2"/>
       <c r="AC7" s="2"/>
     </row>
     <row r="8" spans="2:39" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="C8" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="45"/>
-      <c r="E8" s="46" t="s">
+      <c r="D8" s="42"/>
+      <c r="E8" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="60">
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="52">
         <v>46073</v>
       </c>
-      <c r="J8" s="60"/>
-      <c r="K8" s="61" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" s="61"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
-      <c r="S8" s="16"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="16"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="16"/>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="16"/>
-      <c r="Z8" s="16"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8" s="41"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="13"/>
       <c r="AA8" s="2"/>
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
     </row>
-    <row r="9" spans="2:39" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="44" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="44"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="44"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
-      <c r="Y9" s="2"/>
-      <c r="Z9" s="2"/>
+    <row r="9" spans="2:39" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="69" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="42"/>
+      <c r="E9" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="52">
+        <v>47169</v>
+      </c>
+      <c r="J9" s="52"/>
+      <c r="K9" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" s="42"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="13"/>
+      <c r="U9" s="13"/>
+      <c r="V9" s="13"/>
+      <c r="W9" s="13"/>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="13"/>
+      <c r="Z9" s="13"/>
       <c r="AA9" s="2"/>
       <c r="AB9" s="2"/>
       <c r="AC9" s="2"/>
     </row>
-    <row r="10" spans="2:39" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="K10" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="L10" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="O10" s="59"/>
-      <c r="P10" s="59"/>
-      <c r="Q10" s="59"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="6"/>
-      <c r="T10" s="59"/>
-      <c r="U10" s="59"/>
-      <c r="V10" s="59"/>
-      <c r="W10" s="6"/>
-      <c r="X10" s="59"/>
-      <c r="Y10" s="59"/>
-      <c r="Z10" s="59"/>
+    <row r="10" spans="2:39" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="69" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="42"/>
+      <c r="E10" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="52">
+        <v>48264</v>
+      </c>
+      <c r="J10" s="52"/>
+      <c r="K10" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="L10" s="41"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="13"/>
+      <c r="U10" s="13"/>
+      <c r="V10" s="13"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="13"/>
+      <c r="Y10" s="13"/>
+      <c r="Z10" s="13"/>
       <c r="AA10" s="2"/>
       <c r="AB10" s="2"/>
       <c r="AC10" s="2"/>
-      <c r="AD10" s="4"/>
-      <c r="AE10" s="4"/>
-      <c r="AF10" s="4"/>
-      <c r="AG10" s="4"/>
-      <c r="AH10" s="4"/>
-      <c r="AI10" s="4"/>
-      <c r="AJ10" s="4"/>
-      <c r="AK10" s="4"/>
-      <c r="AL10" s="4"/>
-      <c r="AM10" s="4"/>
     </row>
-    <row r="11" spans="2:39" s="32" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="26" t="s">
+    <row r="11" spans="2:39" s="1" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="51" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="51"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="2"/>
+      <c r="Z11" s="2"/>
+      <c r="AA11" s="2"/>
+      <c r="AB11" s="2"/>
+      <c r="AC11" s="2"/>
+    </row>
+    <row r="12" spans="2:39" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="O12" s="50"/>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="36"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="50"/>
+      <c r="V12" s="50"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="50"/>
+      <c r="Y12" s="50"/>
+      <c r="Z12" s="50"/>
+      <c r="AA12" s="2"/>
+      <c r="AB12" s="2"/>
+      <c r="AC12" s="2"/>
+      <c r="AD12" s="4"/>
+      <c r="AE12" s="4"/>
+      <c r="AF12" s="4"/>
+      <c r="AG12" s="4"/>
+      <c r="AH12" s="4"/>
+      <c r="AI12" s="4"/>
+      <c r="AJ12" s="4"/>
+      <c r="AK12" s="4"/>
+      <c r="AL12" s="4"/>
+      <c r="AM12" s="4"/>
+    </row>
+    <row r="13" spans="2:39" s="28" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="D13" s="67" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="68">
+        <v>43881</v>
+      </c>
+      <c r="F13" s="68">
+        <v>44252</v>
+      </c>
+      <c r="G13" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="28">
-        <v>43881</v>
-      </c>
-      <c r="F11" s="28">
-        <v>44252</v>
-      </c>
-      <c r="G11" s="45" t="s">
+      <c r="K13" s="25"/>
+      <c r="L13" s="37"/>
+      <c r="O13" s="27"/>
+      <c r="P13" s="27"/>
+      <c r="Q13" s="27"/>
+      <c r="R13" s="27"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="27"/>
+      <c r="U13" s="27"/>
+      <c r="V13" s="27"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="27"/>
+      <c r="Y13" s="27"/>
+      <c r="Z13" s="27"/>
+      <c r="AA13" s="29"/>
+      <c r="AB13" s="29"/>
+      <c r="AC13" s="29"/>
+      <c r="AD13" s="30"/>
+      <c r="AE13" s="30"/>
+      <c r="AF13" s="30"/>
+      <c r="AG13" s="30"/>
+      <c r="AH13" s="30"/>
+      <c r="AI13" s="30"/>
+      <c r="AJ13" s="30"/>
+      <c r="AK13" s="30"/>
+      <c r="AL13" s="30"/>
+      <c r="AM13" s="30"/>
+    </row>
+    <row r="14" spans="2:39" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="66" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="67" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="67" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="68">
+        <v>44253</v>
+      </c>
+      <c r="F14" s="68">
+        <v>44617</v>
+      </c>
+      <c r="G14" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="65" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="25"/>
+      <c r="L14" s="37"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="27"/>
+      <c r="Q14" s="27"/>
+      <c r="R14" s="27"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="27"/>
+      <c r="U14" s="27"/>
+      <c r="V14" s="27"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="27"/>
+      <c r="Y14" s="27"/>
+      <c r="Z14" s="27"/>
+      <c r="AA14" s="29"/>
+      <c r="AB14" s="29"/>
+      <c r="AC14" s="29"/>
+      <c r="AD14" s="30"/>
+      <c r="AE14" s="30"/>
+      <c r="AF14" s="30"/>
+      <c r="AG14" s="30"/>
+      <c r="AH14" s="30"/>
+      <c r="AI14" s="30"/>
+      <c r="AJ14" s="30"/>
+      <c r="AK14" s="30"/>
+      <c r="AL14" s="30"/>
+      <c r="AM14" s="30"/>
+    </row>
+    <row r="15" spans="2:39" s="28" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="19" t="s">
+      <c r="D15" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="K11" s="36"/>
-      <c r="L11" s="35"/>
-      <c r="O11" s="30"/>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="30"/>
-      <c r="R11" s="30"/>
-      <c r="S11" s="6"/>
-      <c r="T11" s="30"/>
-      <c r="U11" s="30"/>
-      <c r="V11" s="30"/>
-      <c r="W11" s="6"/>
-      <c r="X11" s="30"/>
-      <c r="Y11" s="30"/>
-      <c r="Z11" s="30"/>
-      <c r="AA11" s="33"/>
-      <c r="AB11" s="33"/>
-      <c r="AC11" s="33"/>
-      <c r="AD11" s="34"/>
-      <c r="AE11" s="34"/>
-      <c r="AF11" s="34"/>
-      <c r="AG11" s="34"/>
-      <c r="AH11" s="34"/>
-      <c r="AI11" s="34"/>
-      <c r="AJ11" s="34"/>
-      <c r="AK11" s="34"/>
-      <c r="AL11" s="34"/>
-      <c r="AM11" s="34"/>
+      <c r="E15" s="68">
+        <v>44647</v>
+      </c>
+      <c r="F15" s="68">
+        <v>45347</v>
+      </c>
+      <c r="G15" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="K15" s="25"/>
+      <c r="L15" s="37"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="27"/>
+      <c r="R15" s="27"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="27"/>
+      <c r="U15" s="27"/>
+      <c r="V15" s="27"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="27"/>
+      <c r="Y15" s="27"/>
+      <c r="Z15" s="27"/>
+      <c r="AA15" s="29"/>
+      <c r="AB15" s="29"/>
+      <c r="AC15" s="29"/>
+      <c r="AD15" s="30"/>
+      <c r="AE15" s="30"/>
+      <c r="AF15" s="30"/>
+      <c r="AG15" s="30"/>
+      <c r="AH15" s="30"/>
+      <c r="AI15" s="30"/>
+      <c r="AJ15" s="30"/>
+      <c r="AK15" s="30"/>
+      <c r="AL15" s="30"/>
+      <c r="AM15" s="30"/>
     </row>
-    <row r="12" spans="2:39" s="32" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="28">
-        <v>44253</v>
-      </c>
-      <c r="F12" s="28">
-        <v>44617</v>
-      </c>
-      <c r="G12" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="K12" s="29"/>
-      <c r="L12" s="40"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="31"/>
-      <c r="Q12" s="31"/>
-      <c r="R12" s="31"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="31"/>
-      <c r="U12" s="31"/>
-      <c r="V12" s="31"/>
-      <c r="W12" s="6"/>
-      <c r="X12" s="31"/>
-      <c r="Y12" s="31"/>
-      <c r="Z12" s="31"/>
-      <c r="AA12" s="33"/>
-      <c r="AB12" s="33"/>
-      <c r="AC12" s="33"/>
-      <c r="AD12" s="34"/>
-      <c r="AE12" s="34"/>
-      <c r="AF12" s="34"/>
-      <c r="AG12" s="34"/>
-      <c r="AH12" s="34"/>
-      <c r="AI12" s="34"/>
-      <c r="AJ12" s="34"/>
-      <c r="AK12" s="34"/>
-      <c r="AL12" s="34"/>
-      <c r="AM12" s="34"/>
+    <row r="16" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="22"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="37"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="26"/>
+      <c r="R16" s="26"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="26"/>
+      <c r="U16" s="26"/>
+      <c r="V16" s="26"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="26"/>
+      <c r="Y16" s="26"/>
+      <c r="Z16" s="26"/>
+      <c r="AA16" s="29"/>
+      <c r="AB16" s="29"/>
+      <c r="AC16" s="29"/>
+      <c r="AD16" s="30"/>
+      <c r="AE16" s="30"/>
+      <c r="AF16" s="30"/>
+      <c r="AG16" s="30"/>
+      <c r="AH16" s="30"/>
+      <c r="AI16" s="30"/>
+      <c r="AJ16" s="30"/>
+      <c r="AK16" s="30"/>
+      <c r="AL16" s="30"/>
+      <c r="AM16" s="30"/>
     </row>
-    <row r="13" spans="2:39" s="32" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="28">
-        <v>44647</v>
-      </c>
-      <c r="F13" s="28">
-        <v>45347</v>
-      </c>
-      <c r="G13" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="K13" s="29"/>
-      <c r="L13" s="40"/>
-      <c r="O13" s="31"/>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="31"/>
-      <c r="R13" s="31"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="31"/>
-      <c r="U13" s="31"/>
-      <c r="V13" s="31"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="31"/>
-      <c r="Y13" s="31"/>
-      <c r="Z13" s="31"/>
-      <c r="AA13" s="33"/>
-      <c r="AB13" s="33"/>
-      <c r="AC13" s="33"/>
-      <c r="AD13" s="34"/>
-      <c r="AE13" s="34"/>
-      <c r="AF13" s="34"/>
-      <c r="AG13" s="34"/>
-      <c r="AH13" s="34"/>
-      <c r="AI13" s="34"/>
-      <c r="AJ13" s="34"/>
-      <c r="AK13" s="34"/>
-      <c r="AL13" s="34"/>
-      <c r="AM13" s="34"/>
+    <row r="17" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="22"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="37"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="5"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="31"/>
+      <c r="Z17" s="31"/>
+      <c r="AA17" s="29"/>
+      <c r="AB17" s="29"/>
+      <c r="AC17" s="29"/>
+      <c r="AD17" s="30"/>
+      <c r="AE17" s="30"/>
+      <c r="AF17" s="30"/>
+      <c r="AG17" s="30"/>
+      <c r="AH17" s="30"/>
+      <c r="AI17" s="30"/>
+      <c r="AJ17" s="30"/>
+      <c r="AK17" s="30"/>
+      <c r="AL17" s="30"/>
+      <c r="AM17" s="30"/>
     </row>
-    <row r="14" spans="2:39" s="32" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="26"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="35"/>
-      <c r="O14" s="31"/>
-      <c r="P14" s="31"/>
-      <c r="Q14" s="31"/>
-      <c r="R14" s="31"/>
-      <c r="S14" s="6"/>
-      <c r="T14" s="31"/>
-      <c r="U14" s="31"/>
-      <c r="V14" s="31"/>
-      <c r="W14" s="6"/>
-      <c r="X14" s="31"/>
-      <c r="Y14" s="31"/>
-      <c r="Z14" s="31"/>
-      <c r="AA14" s="33"/>
-      <c r="AB14" s="33"/>
-      <c r="AC14" s="33"/>
-      <c r="AD14" s="34"/>
-      <c r="AE14" s="34"/>
-      <c r="AF14" s="34"/>
-      <c r="AG14" s="34"/>
-      <c r="AH14" s="34"/>
-      <c r="AI14" s="34"/>
-      <c r="AJ14" s="34"/>
-      <c r="AK14" s="34"/>
-      <c r="AL14" s="34"/>
-      <c r="AM14" s="34"/>
+    <row r="18" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="22"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="37"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="36"/>
+      <c r="U18" s="36"/>
+      <c r="V18" s="36"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="36"/>
+      <c r="Y18" s="36"/>
+      <c r="Z18" s="36"/>
+      <c r="AA18" s="29"/>
+      <c r="AB18" s="29"/>
+      <c r="AC18" s="29"/>
+      <c r="AD18" s="30"/>
+      <c r="AE18" s="30"/>
+      <c r="AF18" s="30"/>
+      <c r="AG18" s="30"/>
+      <c r="AH18" s="30"/>
+      <c r="AI18" s="30"/>
+      <c r="AJ18" s="30"/>
+      <c r="AK18" s="30"/>
+      <c r="AL18" s="30"/>
+      <c r="AM18" s="30"/>
     </row>
-    <row r="15" spans="2:39" s="32" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="26"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="35"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="6"/>
-      <c r="T15" s="31"/>
-      <c r="U15" s="31"/>
-      <c r="V15" s="31"/>
-      <c r="W15" s="6"/>
-      <c r="X15" s="31"/>
-      <c r="Y15" s="31"/>
-      <c r="Z15" s="31"/>
-      <c r="AA15" s="33"/>
-      <c r="AB15" s="33"/>
-      <c r="AC15" s="33"/>
-      <c r="AD15" s="34"/>
-      <c r="AE15" s="34"/>
-      <c r="AF15" s="34"/>
-      <c r="AG15" s="34"/>
-      <c r="AH15" s="34"/>
-      <c r="AI15" s="34"/>
-      <c r="AJ15" s="34"/>
-      <c r="AK15" s="34"/>
-      <c r="AL15" s="34"/>
-      <c r="AM15" s="34"/>
+    <row r="19" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="22"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="37"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="36"/>
+      <c r="U19" s="36"/>
+      <c r="V19" s="36"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="36"/>
+      <c r="Y19" s="36"/>
+      <c r="Z19" s="36"/>
+      <c r="AA19" s="29"/>
+      <c r="AB19" s="29"/>
+      <c r="AC19" s="29"/>
+      <c r="AD19" s="30"/>
+      <c r="AE19" s="30"/>
+      <c r="AF19" s="30"/>
+      <c r="AG19" s="30"/>
+      <c r="AH19" s="30"/>
+      <c r="AI19" s="30"/>
+      <c r="AJ19" s="30"/>
+      <c r="AK19" s="30"/>
+      <c r="AL19" s="30"/>
+      <c r="AM19" s="30"/>
     </row>
-    <row r="16" spans="2:39" s="32" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="26"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="35"/>
-      <c r="O16" s="30"/>
-      <c r="P16" s="30"/>
-      <c r="Q16" s="30"/>
-      <c r="R16" s="30"/>
-      <c r="S16" s="6"/>
-      <c r="T16" s="30"/>
-      <c r="U16" s="30"/>
-      <c r="V16" s="30"/>
-      <c r="W16" s="6"/>
-      <c r="X16" s="30"/>
-      <c r="Y16" s="30"/>
-      <c r="Z16" s="30"/>
-      <c r="AA16" s="33"/>
-      <c r="AB16" s="33"/>
-      <c r="AC16" s="33"/>
-      <c r="AD16" s="34"/>
-      <c r="AE16" s="34"/>
-      <c r="AF16" s="34"/>
-      <c r="AG16" s="34"/>
-      <c r="AH16" s="34"/>
-      <c r="AI16" s="34"/>
-      <c r="AJ16" s="34"/>
-      <c r="AK16" s="34"/>
-      <c r="AL16" s="34"/>
-      <c r="AM16" s="34"/>
+    <row r="20" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="22"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="37"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="36"/>
+      <c r="U20" s="36"/>
+      <c r="V20" s="36"/>
+      <c r="W20" s="5"/>
+      <c r="X20" s="36"/>
+      <c r="Y20" s="36"/>
+      <c r="Z20" s="36"/>
+      <c r="AA20" s="29"/>
+      <c r="AB20" s="29"/>
+      <c r="AC20" s="29"/>
+      <c r="AD20" s="30"/>
+      <c r="AE20" s="30"/>
+      <c r="AF20" s="30"/>
+      <c r="AG20" s="30"/>
+      <c r="AH20" s="30"/>
+      <c r="AI20" s="30"/>
+      <c r="AJ20" s="30"/>
+      <c r="AK20" s="30"/>
+      <c r="AL20" s="30"/>
+      <c r="AM20" s="30"/>
     </row>
-    <row r="17" spans="2:39" s="32" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="26"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="38"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="37"/>
-      <c r="S17" s="6"/>
-      <c r="T17" s="37"/>
-      <c r="U17" s="37"/>
-      <c r="V17" s="37"/>
-      <c r="W17" s="6"/>
-      <c r="X17" s="37"/>
-      <c r="Y17" s="37"/>
-      <c r="Z17" s="37"/>
-      <c r="AA17" s="33"/>
-      <c r="AB17" s="33"/>
-      <c r="AC17" s="33"/>
-      <c r="AD17" s="34"/>
-      <c r="AE17" s="34"/>
-      <c r="AF17" s="34"/>
-      <c r="AG17" s="34"/>
-      <c r="AH17" s="34"/>
-      <c r="AI17" s="34"/>
-      <c r="AJ17" s="34"/>
-      <c r="AK17" s="34"/>
-      <c r="AL17" s="34"/>
-      <c r="AM17" s="34"/>
+    <row r="21" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="22"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="37"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="36"/>
+      <c r="U21" s="36"/>
+      <c r="V21" s="36"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="36"/>
+      <c r="Y21" s="36"/>
+      <c r="Z21" s="36"/>
+      <c r="AA21" s="29"/>
+      <c r="AB21" s="29"/>
+      <c r="AC21" s="29"/>
+      <c r="AD21" s="30"/>
+      <c r="AE21" s="30"/>
+      <c r="AF21" s="30"/>
+      <c r="AG21" s="30"/>
+      <c r="AH21" s="30"/>
+      <c r="AI21" s="30"/>
+      <c r="AJ21" s="30"/>
+      <c r="AK21" s="30"/>
+      <c r="AL21" s="30"/>
+      <c r="AM21" s="30"/>
     </row>
-    <row r="18" spans="2:39" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="49" t="s">
+    <row r="22" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="22"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="37"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="36"/>
+      <c r="U22" s="36"/>
+      <c r="V22" s="36"/>
+      <c r="W22" s="5"/>
+      <c r="X22" s="36"/>
+      <c r="Y22" s="36"/>
+      <c r="Z22" s="36"/>
+      <c r="AA22" s="29"/>
+      <c r="AB22" s="29"/>
+      <c r="AC22" s="29"/>
+      <c r="AD22" s="30"/>
+      <c r="AE22" s="30"/>
+      <c r="AF22" s="30"/>
+      <c r="AG22" s="30"/>
+      <c r="AH22" s="30"/>
+      <c r="AI22" s="30"/>
+      <c r="AJ22" s="30"/>
+      <c r="AK22" s="30"/>
+      <c r="AL22" s="30"/>
+      <c r="AM22" s="30"/>
+    </row>
+    <row r="23" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="22"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="37"/>
+      <c r="O23" s="36"/>
+      <c r="P23" s="36"/>
+      <c r="Q23" s="36"/>
+      <c r="R23" s="36"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="36"/>
+      <c r="U23" s="36"/>
+      <c r="V23" s="36"/>
+      <c r="W23" s="5"/>
+      <c r="X23" s="36"/>
+      <c r="Y23" s="36"/>
+      <c r="Z23" s="36"/>
+      <c r="AA23" s="29"/>
+      <c r="AB23" s="29"/>
+      <c r="AC23" s="29"/>
+      <c r="AD23" s="30"/>
+      <c r="AE23" s="30"/>
+      <c r="AF23" s="30"/>
+      <c r="AG23" s="30"/>
+      <c r="AH23" s="30"/>
+      <c r="AI23" s="30"/>
+      <c r="AJ23" s="30"/>
+      <c r="AK23" s="30"/>
+      <c r="AL23" s="30"/>
+      <c r="AM23" s="30"/>
+    </row>
+    <row r="24" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="22"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="37"/>
+      <c r="O24" s="36"/>
+      <c r="P24" s="36"/>
+      <c r="Q24" s="36"/>
+      <c r="R24" s="36"/>
+      <c r="S24" s="5"/>
+      <c r="T24" s="36"/>
+      <c r="U24" s="36"/>
+      <c r="V24" s="36"/>
+      <c r="W24" s="5"/>
+      <c r="X24" s="36"/>
+      <c r="Y24" s="36"/>
+      <c r="Z24" s="36"/>
+      <c r="AA24" s="29"/>
+      <c r="AB24" s="29"/>
+      <c r="AC24" s="29"/>
+      <c r="AD24" s="30"/>
+      <c r="AE24" s="30"/>
+      <c r="AF24" s="30"/>
+      <c r="AG24" s="30"/>
+      <c r="AH24" s="30"/>
+      <c r="AI24" s="30"/>
+      <c r="AJ24" s="30"/>
+      <c r="AK24" s="30"/>
+      <c r="AL24" s="30"/>
+      <c r="AM24" s="30"/>
+    </row>
+    <row r="25" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="22"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="37"/>
+      <c r="O25" s="36"/>
+      <c r="P25" s="36"/>
+      <c r="Q25" s="36"/>
+      <c r="R25" s="36"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="36"/>
+      <c r="U25" s="36"/>
+      <c r="V25" s="36"/>
+      <c r="W25" s="5"/>
+      <c r="X25" s="36"/>
+      <c r="Y25" s="36"/>
+      <c r="Z25" s="36"/>
+      <c r="AA25" s="29"/>
+      <c r="AB25" s="29"/>
+      <c r="AC25" s="29"/>
+      <c r="AD25" s="30"/>
+      <c r="AE25" s="30"/>
+      <c r="AF25" s="30"/>
+      <c r="AG25" s="30"/>
+      <c r="AH25" s="30"/>
+      <c r="AI25" s="30"/>
+      <c r="AJ25" s="30"/>
+      <c r="AK25" s="30"/>
+      <c r="AL25" s="30"/>
+      <c r="AM25" s="30"/>
+    </row>
+    <row r="26" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="22"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="37"/>
+      <c r="O26" s="36"/>
+      <c r="P26" s="36"/>
+      <c r="Q26" s="36"/>
+      <c r="R26" s="36"/>
+      <c r="S26" s="5"/>
+      <c r="T26" s="36"/>
+      <c r="U26" s="36"/>
+      <c r="V26" s="36"/>
+      <c r="W26" s="5"/>
+      <c r="X26" s="36"/>
+      <c r="Y26" s="36"/>
+      <c r="Z26" s="36"/>
+      <c r="AA26" s="29"/>
+      <c r="AB26" s="29"/>
+      <c r="AC26" s="29"/>
+      <c r="AD26" s="30"/>
+      <c r="AE26" s="30"/>
+      <c r="AF26" s="30"/>
+      <c r="AG26" s="30"/>
+      <c r="AH26" s="30"/>
+      <c r="AI26" s="30"/>
+      <c r="AJ26" s="30"/>
+      <c r="AK26" s="30"/>
+      <c r="AL26" s="30"/>
+      <c r="AM26" s="30"/>
+    </row>
+    <row r="27" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="22"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="37"/>
+      <c r="O27" s="36"/>
+      <c r="P27" s="36"/>
+      <c r="Q27" s="36"/>
+      <c r="R27" s="36"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="36"/>
+      <c r="U27" s="36"/>
+      <c r="V27" s="36"/>
+      <c r="W27" s="5"/>
+      <c r="X27" s="36"/>
+      <c r="Y27" s="36"/>
+      <c r="Z27" s="36"/>
+      <c r="AA27" s="29"/>
+      <c r="AB27" s="29"/>
+      <c r="AC27" s="29"/>
+      <c r="AD27" s="30"/>
+      <c r="AE27" s="30"/>
+      <c r="AF27" s="30"/>
+      <c r="AG27" s="30"/>
+      <c r="AH27" s="30"/>
+      <c r="AI27" s="30"/>
+      <c r="AJ27" s="30"/>
+      <c r="AK27" s="30"/>
+      <c r="AL27" s="30"/>
+      <c r="AM27" s="30"/>
+    </row>
+    <row r="28" spans="2:39" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B28" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="51"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="7"/>
-      <c r="AA18" s="9"/>
-      <c r="AB18" s="4"/>
-      <c r="AC18" s="4"/>
-      <c r="AD18" s="4"/>
-      <c r="AE18" s="4"/>
-      <c r="AF18" s="4"/>
-      <c r="AG18" s="4"/>
-      <c r="AH18" s="4"/>
-      <c r="AI18" s="4"/>
-      <c r="AJ18" s="4"/>
-      <c r="AK18" s="4"/>
-      <c r="AL18" s="4"/>
-      <c r="AM18" s="4"/>
+      <c r="C28" s="62"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="63"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
+      <c r="Q28" s="6"/>
+      <c r="R28" s="6"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="6"/>
+      <c r="U28" s="6"/>
+      <c r="V28" s="6"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="6"/>
+      <c r="Y28" s="6"/>
+      <c r="Z28" s="6"/>
+      <c r="AA28" s="8"/>
+      <c r="AB28" s="4"/>
+      <c r="AC28" s="4"/>
+      <c r="AD28" s="4"/>
+      <c r="AE28" s="4"/>
+      <c r="AF28" s="4"/>
+      <c r="AG28" s="4"/>
+      <c r="AH28" s="4"/>
+      <c r="AI28" s="4"/>
+      <c r="AJ28" s="4"/>
+      <c r="AK28" s="4"/>
+      <c r="AL28" s="4"/>
+      <c r="AM28" s="4"/>
     </row>
-    <row r="19" spans="2:39" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B19" s="49" t="s">
+    <row r="29" spans="2:39" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B29" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="8"/>
-      <c r="T19" s="10"/>
-      <c r="U19" s="10"/>
-      <c r="V19" s="10"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="7"/>
-      <c r="Z19" s="7"/>
-      <c r="AA19" s="4"/>
-      <c r="AB19" s="4"/>
-      <c r="AC19" s="4"/>
-      <c r="AD19" s="4"/>
-      <c r="AE19" s="4"/>
-      <c r="AF19" s="4"/>
-      <c r="AG19" s="4"/>
-      <c r="AH19" s="4"/>
-      <c r="AI19" s="4"/>
-      <c r="AJ19" s="4"/>
-      <c r="AK19" s="4"/>
-      <c r="AL19" s="4"/>
-      <c r="AM19" s="4"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="63"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="21"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="W29" s="3"/>
+      <c r="X29" s="6"/>
+      <c r="Y29" s="6"/>
+      <c r="Z29" s="6"/>
+      <c r="AA29" s="4"/>
+      <c r="AB29" s="4"/>
+      <c r="AC29" s="4"/>
+      <c r="AD29" s="4"/>
+      <c r="AE29" s="4"/>
+      <c r="AF29" s="4"/>
+      <c r="AG29" s="4"/>
+      <c r="AH29" s="4"/>
+      <c r="AI29" s="4"/>
+      <c r="AJ29" s="4"/>
+      <c r="AK29" s="4"/>
+      <c r="AL29" s="4"/>
+      <c r="AM29" s="4"/>
     </row>
-    <row r="20" spans="2:39" s="1" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="47" t="s">
+    <row r="30" spans="2:39" s="1" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="48"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="48"/>
-      <c r="K20" s="48"/>
-      <c r="L20" s="48"/>
-      <c r="N20" s="12"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
-      <c r="Y20" s="2"/>
-      <c r="Z20" s="2"/>
-      <c r="AA20" s="4"/>
-      <c r="AB20" s="4"/>
-      <c r="AC20" s="4"/>
-      <c r="AD20" s="4"/>
-      <c r="AE20" s="4"/>
-      <c r="AF20" s="4"/>
-      <c r="AG20" s="4"/>
-      <c r="AH20" s="4"/>
-      <c r="AI20" s="4"/>
-      <c r="AJ20" s="4"/>
-      <c r="AK20" s="4"/>
-      <c r="AL20" s="4"/>
-      <c r="AM20" s="4"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="56"/>
+      <c r="K30" s="56"/>
+      <c r="L30" s="57"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="12"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+      <c r="Y30" s="2"/>
+      <c r="Z30" s="2"/>
+      <c r="AA30" s="4"/>
+      <c r="AB30" s="4"/>
+      <c r="AC30" s="4"/>
+      <c r="AD30" s="4"/>
+      <c r="AE30" s="4"/>
+      <c r="AF30" s="4"/>
+      <c r="AG30" s="4"/>
+      <c r="AH30" s="4"/>
+      <c r="AI30" s="4"/>
+      <c r="AJ30" s="4"/>
+      <c r="AK30" s="4"/>
+      <c r="AL30" s="4"/>
+      <c r="AM30" s="4"/>
     </row>
-    <row r="21" spans="2:39" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="47"/>
-      <c r="C21" s="48"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="48"/>
-      <c r="J21" s="48"/>
-      <c r="K21" s="48"/>
-      <c r="L21" s="48"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
-      <c r="X21" s="2"/>
-      <c r="Y21" s="2"/>
-      <c r="Z21" s="2"/>
-      <c r="AA21" s="4"/>
-      <c r="AB21" s="4"/>
-      <c r="AC21" s="4"/>
-      <c r="AD21" s="4"/>
-      <c r="AE21" s="4"/>
-      <c r="AF21" s="4"/>
-      <c r="AG21" s="4"/>
-      <c r="AH21" s="4"/>
-      <c r="AI21" s="4"/>
-      <c r="AJ21" s="4"/>
-      <c r="AK21" s="4"/>
-      <c r="AL21" s="4"/>
-      <c r="AM21" s="4"/>
-    </row>
-    <row r="22" spans="2:39" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="2"/>
-      <c r="W22" s="2"/>
-      <c r="X22" s="2"/>
-      <c r="Y22" s="2"/>
-      <c r="Z22" s="2"/>
-    </row>
-    <row r="23" spans="2:39" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="O23" s="2"/>
-      <c r="P23" s="14"/>
-      <c r="Q23" s="14"/>
-      <c r="R23" s="14"/>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
-      <c r="V23" s="2"/>
-      <c r="W23" s="2"/>
-      <c r="X23" s="15"/>
-      <c r="Y23" s="2"/>
-      <c r="Z23" s="2"/>
-    </row>
-    <row r="24" spans="2:39" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="O24" s="2"/>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
-      <c r="Y24" s="2"/>
-      <c r="Z24" s="2"/>
+    <row r="31" spans="2:39" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="54"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="59"/>
+      <c r="K31" s="59"/>
+      <c r="L31" s="60"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="Y31" s="2"/>
+      <c r="Z31" s="2"/>
+      <c r="AA31" s="4"/>
+      <c r="AB31" s="4"/>
+      <c r="AC31" s="4"/>
+      <c r="AD31" s="4"/>
+      <c r="AE31" s="4"/>
+      <c r="AF31" s="4"/>
+      <c r="AG31" s="4"/>
+      <c r="AH31" s="4"/>
+      <c r="AI31" s="4"/>
+      <c r="AJ31" s="4"/>
+      <c r="AK31" s="4"/>
+      <c r="AL31" s="4"/>
+      <c r="AM31" s="4"/>
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange password="C71F" sqref="O9:Z19" name="Aralık1_1"/>
+    <protectedRange password="C71F" sqref="O11:Z29" name="Aralık1_1"/>
   </protectedRanges>
-  <mergeCells count="35">
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="X10:Z10"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="T10:V10"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:H5"/>
+  <mergeCells count="51">
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="I7:J7"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="E6:H6"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="K6:L6"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:L21"/>
-    <mergeCell ref="B9:L9"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:L31"/>
+    <mergeCell ref="B11:L11"/>
+    <mergeCell ref="B28:J28"/>
     <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="B29:J29"/>
     <mergeCell ref="G13:I13"/>
     <mergeCell ref="G14:I14"/>
-    <mergeCell ref="B18:J18"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="B19:J19"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="X12:Z12"/>
+    <mergeCell ref="O12:Q12"/>
+    <mergeCell ref="T12:V12"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G18:I18"/>
   </mergeCells>
-  <conditionalFormatting sqref="J10:K10 K11 K16">
-    <cfRule type="cellIs" dxfId="56" priority="151" operator="equal">
-      <formula>"h"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="152" operator="equal">
-      <formula>"k"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="153" operator="equal">
-      <formula>"e"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J11">
-    <cfRule type="cellIs" dxfId="53" priority="85" operator="equal">
-      <formula>"h"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="86" operator="equal">
-      <formula>"k"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="87" operator="equal">
+  <conditionalFormatting sqref="J12:K12 K16">
+    <cfRule type="cellIs" dxfId="143" priority="247" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="142" priority="248" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="141" priority="249" operator="equal">
       <formula>"e"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J16">
-    <cfRule type="cellIs" dxfId="50" priority="82" operator="equal">
-      <formula>"h"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="83" operator="equal">
-      <formula>"k"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="84" operator="equal">
+    <cfRule type="cellIs" dxfId="140" priority="178" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="139" priority="179" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="138" priority="180" operator="equal">
       <formula>"e"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6">
-    <cfRule type="cellIs" dxfId="47" priority="76" operator="equal">
-      <formula>"h"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="77" operator="equal">
-      <formula>"k"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="78" operator="equal">
+    <cfRule type="cellIs" dxfId="137" priority="172" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="136" priority="173" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="135" priority="174" operator="equal">
       <formula>"e"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="44" priority="64" operator="equal">
-      <formula>"h"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="65" operator="equal">
-      <formula>"k"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="66" operator="equal">
-      <formula>"e"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K12">
-    <cfRule type="cellIs" dxfId="41" priority="55" operator="equal">
-      <formula>"h"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="56" operator="equal">
-      <formula>"k"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="134" priority="160" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="133" priority="161" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="132" priority="162" operator="equal">
       <formula>"e"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K15">
-    <cfRule type="cellIs" dxfId="38" priority="49" operator="equal">
-      <formula>"h"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="50" operator="equal">
-      <formula>"k"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="51" operator="equal">
+    <cfRule type="cellIs" dxfId="131" priority="145" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="130" priority="146" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="129" priority="147" operator="equal">
       <formula>"e"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15">
-    <cfRule type="cellIs" dxfId="35" priority="46" operator="equal">
-      <formula>"h"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="47" operator="equal">
-      <formula>"k"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="128" priority="142" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="127" priority="143" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="126" priority="144" operator="equal">
       <formula>"e"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K14">
-    <cfRule type="cellIs" dxfId="32" priority="43" operator="equal">
-      <formula>"h"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="44" operator="equal">
-      <formula>"k"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="125" priority="139" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="124" priority="140" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="123" priority="141" operator="equal">
       <formula>"e"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J14">
-    <cfRule type="cellIs" dxfId="29" priority="40" operator="equal">
-      <formula>"h"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="41" operator="equal">
-      <formula>"k"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="122" priority="136" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="121" priority="137" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="120" priority="138" operator="equal">
       <formula>"e"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="cellIs" dxfId="26" priority="37" operator="equal">
-      <formula>"h"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="38" operator="equal">
-      <formula>"k"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="133" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="118" priority="134" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="117" priority="135" operator="equal">
       <formula>"e"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J13">
-    <cfRule type="cellIs" dxfId="23" priority="34" operator="equal">
-      <formula>"h"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="35" operator="equal">
-      <formula>"k"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="116" priority="130" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="115" priority="131" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="114" priority="132" operator="equal">
       <formula>"e"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L16">
-    <cfRule type="cellIs" dxfId="20" priority="31" operator="equal">
-      <formula>"h"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="32" operator="equal">
-      <formula>"k"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="127" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="112" priority="128" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="111" priority="129" operator="equal">
       <formula>"e"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L15">
-    <cfRule type="cellIs" dxfId="17" priority="28" operator="equal">
-      <formula>"h"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="29" operator="equal">
-      <formula>"k"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="124" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="109" priority="125" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="108" priority="126" operator="equal">
       <formula>"e"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8">
-    <cfRule type="cellIs" dxfId="14" priority="25" operator="equal">
-      <formula>"h"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="26" operator="equal">
-      <formula>"k"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="121" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="106" priority="122" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="105" priority="123" operator="equal">
       <formula>"e"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K17">
-    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
-      <formula>"h"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="14" operator="equal">
-      <formula>"k"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="109" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="103" priority="110" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="102" priority="111" operator="equal">
       <formula>"e"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L17">
+    <cfRule type="cellIs" dxfId="101" priority="103" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="100" priority="104" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="99" priority="105" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J17">
+    <cfRule type="cellIs" dxfId="98" priority="97" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="97" priority="98" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="96" priority="99" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K27">
+    <cfRule type="cellIs" dxfId="95" priority="94" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="94" priority="95" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="93" priority="96" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L27">
+    <cfRule type="cellIs" dxfId="92" priority="91" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="91" priority="92" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="90" priority="93" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J27">
+    <cfRule type="cellIs" dxfId="89" priority="88" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="88" priority="89" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="87" priority="90" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K26">
+    <cfRule type="cellIs" dxfId="86" priority="85" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="85" priority="86" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="84" priority="87" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L26">
+    <cfRule type="cellIs" dxfId="83" priority="82" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="82" priority="83" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="81" priority="84" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J26">
+    <cfRule type="cellIs" dxfId="80" priority="79" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="79" priority="80" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="78" priority="81" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K25">
+    <cfRule type="cellIs" dxfId="77" priority="76" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="77" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="75" priority="78" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L25">
+    <cfRule type="cellIs" dxfId="74" priority="73" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="74" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="75" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J25">
+    <cfRule type="cellIs" dxfId="71" priority="70" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="70" priority="71" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="69" priority="72" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K24">
+    <cfRule type="cellIs" dxfId="68" priority="67" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="67" priority="68" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="66" priority="69" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L24">
+    <cfRule type="cellIs" dxfId="65" priority="64" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="65" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="63" priority="66" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J24">
+    <cfRule type="cellIs" dxfId="62" priority="61" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="62" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="60" priority="63" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K23">
+    <cfRule type="cellIs" dxfId="59" priority="58" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="58" priority="59" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="57" priority="60" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L23">
+    <cfRule type="cellIs" dxfId="56" priority="55" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="55" priority="56" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="54" priority="57" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J23">
+    <cfRule type="cellIs" dxfId="53" priority="52" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="52" priority="53" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="51" priority="54" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K22">
+    <cfRule type="cellIs" dxfId="50" priority="49" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="50" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="48" priority="51" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L22">
+    <cfRule type="cellIs" dxfId="47" priority="46" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="47" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="45" priority="48" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J22">
+    <cfRule type="cellIs" dxfId="44" priority="43" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="43" priority="44" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="45" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K21">
+    <cfRule type="cellIs" dxfId="41" priority="40" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="41" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="39" priority="42" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L21">
+    <cfRule type="cellIs" dxfId="38" priority="37" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="38" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="36" priority="39" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J21">
+    <cfRule type="cellIs" dxfId="35" priority="34" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="35" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="36" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K20">
+    <cfRule type="cellIs" dxfId="32" priority="31" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="32" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="33" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L20">
+    <cfRule type="cellIs" dxfId="29" priority="28" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="29" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="30" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J20">
+    <cfRule type="cellIs" dxfId="26" priority="25" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="26" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="27" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K19">
+    <cfRule type="cellIs" dxfId="23" priority="22" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="23" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="24" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L19">
+    <cfRule type="cellIs" dxfId="20" priority="19" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="20" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="21" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J19">
+    <cfRule type="cellIs" dxfId="17" priority="16" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="18" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K18">
+    <cfRule type="cellIs" dxfId="14" priority="13" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="15" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L18">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
+      <formula>"h"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+      <formula>"k"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
+      <formula>"e"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J18">
     <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
       <formula>"h"</formula>
     </cfRule>
@@ -2604,7 +4245,7 @@
       <formula>"e"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J12">
+  <conditionalFormatting sqref="K9">
     <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>"h"</formula>
     </cfRule>
@@ -2615,7 +4256,7 @@
       <formula>"e"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J17">
+  <conditionalFormatting sqref="K10">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"h"</formula>
     </cfRule>
@@ -2627,16 +4268,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="4a,4b veya 4c'den birini seçiniz" sqref="B11:B17" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="4a,4b veya 4c'den birini seçiniz" sqref="B11:B27" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"4a,4b,4c"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Kadrolu,Proje"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J11:J17" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J11:J27" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"E,K,H"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K6:L8" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K6:L10" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"E,H"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/cikti_taslagi_dolu.xlsx
+++ b/docs/cikti_taslagi_dolu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muhammed.bulut\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2600EB8C-3770-49B8-AD62-ABF4530971C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C23DA0E-9981-426E-82F0-43FDDE623E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,10 +179,10 @@
     <t>Tezli Yüksek Lisans</t>
   </si>
   <si>
-    <t>Yüksek Lisans</t>
-  </si>
-  <si>
     <t>Doktora</t>
+  </si>
+  <si>
+    <t>Tezsiz Yüksek Lisans</t>
   </si>
 </sst>
 </file>
@@ -604,6 +604,72 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -613,15 +679,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -642,63 +699,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2521,13 +2521,13 @@
       <c r="G2" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="44" t="s">
+      <c r="H2" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="46"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="65"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
@@ -2548,11 +2548,11 @@
       <c r="E3" s="19"/>
       <c r="F3" s="34"/>
       <c r="G3" s="35"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="49"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="68"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
@@ -2567,19 +2567,19 @@
       <c r="Z3" s="2"/>
     </row>
     <row r="4" spans="2:39" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
@@ -2598,24 +2598,24 @@
     </row>
     <row r="5" spans="2:39" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="17"/>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51" t="s">
+      <c r="D5" s="47"/>
+      <c r="E5" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51" t="s">
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51" t="s">
+      <c r="J5" s="47"/>
+      <c r="K5" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="L5" s="51"/>
+      <c r="L5" s="47"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
@@ -2633,27 +2633,27 @@
       <c r="AC5" s="2"/>
     </row>
     <row r="6" spans="2:39" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="69" t="s">
+      <c r="B6" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="42"/>
-      <c r="E6" s="43" t="s">
+      <c r="D6" s="43"/>
+      <c r="E6" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="52">
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="45">
         <v>43881</v>
       </c>
-      <c r="J6" s="52"/>
-      <c r="K6" s="42" t="s">
+      <c r="J6" s="45"/>
+      <c r="K6" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="L6" s="42"/>
+      <c r="L6" s="43"/>
       <c r="O6" s="13"/>
       <c r="P6" s="13"/>
       <c r="Q6" s="13"/>
@@ -2671,27 +2671,27 @@
       <c r="AC6" s="2"/>
     </row>
     <row r="7" spans="2:39" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="42"/>
-      <c r="E7" s="43" t="s">
+      <c r="D7" s="43"/>
+      <c r="E7" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="52">
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="45">
         <v>44247</v>
       </c>
-      <c r="J7" s="52"/>
-      <c r="K7" s="42" t="s">
+      <c r="J7" s="45"/>
+      <c r="K7" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="L7" s="42"/>
+      <c r="L7" s="43"/>
       <c r="O7" s="13"/>
       <c r="P7" s="13"/>
       <c r="Q7" s="13"/>
@@ -2709,27 +2709,27 @@
       <c r="AC7" s="2"/>
     </row>
     <row r="8" spans="2:39" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="42"/>
-      <c r="E8" s="43" t="s">
+      <c r="D8" s="43"/>
+      <c r="E8" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="52">
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="45">
         <v>46073</v>
       </c>
-      <c r="J8" s="52"/>
-      <c r="K8" s="41" t="s">
+      <c r="J8" s="45"/>
+      <c r="K8" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="L8" s="41"/>
+      <c r="L8" s="46"/>
       <c r="O8" s="13"/>
       <c r="P8" s="13"/>
       <c r="Q8" s="13"/>
@@ -2747,27 +2747,27 @@
       <c r="AC8" s="2"/>
     </row>
     <row r="9" spans="2:39" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="69" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="42" t="s">
+      <c r="B9" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="42"/>
-      <c r="E9" s="43" t="s">
+      <c r="D9" s="43"/>
+      <c r="E9" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="52">
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="45">
         <v>47169</v>
       </c>
-      <c r="J9" s="52"/>
-      <c r="K9" s="42" t="s">
+      <c r="J9" s="45"/>
+      <c r="K9" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="L9" s="42"/>
+      <c r="L9" s="43"/>
       <c r="O9" s="13"/>
       <c r="P9" s="13"/>
       <c r="Q9" s="13"/>
@@ -2785,27 +2785,27 @@
       <c r="AC9" s="2"/>
     </row>
     <row r="10" spans="2:39" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="69" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="42" t="s">
+      <c r="B10" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="42"/>
-      <c r="E10" s="43" t="s">
+      <c r="D10" s="43"/>
+      <c r="E10" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="52">
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="45">
         <v>48264</v>
       </c>
-      <c r="J10" s="52"/>
-      <c r="K10" s="41" t="s">
+      <c r="J10" s="45"/>
+      <c r="K10" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="L10" s="41"/>
+      <c r="L10" s="46"/>
       <c r="O10" s="13"/>
       <c r="P10" s="13"/>
       <c r="Q10" s="13"/>
@@ -2823,21 +2823,21 @@
       <c r="AC10" s="2"/>
     </row>
     <row r="11" spans="2:39" s="1" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51" t="s">
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="51"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="47"/>
+      <c r="L11" s="47"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
@@ -2870,11 +2870,11 @@
       <c r="F12" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="64" t="s">
+      <c r="G12" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
       <c r="J12" s="14" t="s">
         <v>12</v>
       </c>
@@ -2884,18 +2884,18 @@
       <c r="L12" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="O12" s="50"/>
-      <c r="P12" s="50"/>
-      <c r="Q12" s="50"/>
+      <c r="O12" s="69"/>
+      <c r="P12" s="69"/>
+      <c r="Q12" s="69"/>
       <c r="R12" s="36"/>
       <c r="S12" s="5"/>
-      <c r="T12" s="50"/>
-      <c r="U12" s="50"/>
-      <c r="V12" s="50"/>
+      <c r="T12" s="69"/>
+      <c r="U12" s="69"/>
+      <c r="V12" s="69"/>
       <c r="W12" s="5"/>
-      <c r="X12" s="50"/>
-      <c r="Y12" s="50"/>
-      <c r="Z12" s="50"/>
+      <c r="X12" s="69"/>
+      <c r="Y12" s="69"/>
+      <c r="Z12" s="69"/>
       <c r="AA12" s="2"/>
       <c r="AB12" s="2"/>
       <c r="AC12" s="2"/>
@@ -2911,27 +2911,27 @@
       <c r="AM12" s="4"/>
     </row>
     <row r="13" spans="2:39" s="28" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="67" t="s">
+      <c r="C13" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="67" t="s">
+      <c r="D13" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="68">
+      <c r="E13" s="41">
         <v>43881</v>
       </c>
-      <c r="F13" s="68">
+      <c r="F13" s="41">
         <v>44252</v>
       </c>
-      <c r="G13" s="42" t="s">
+      <c r="G13" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="65" t="s">
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="38" t="s">
         <v>29</v>
       </c>
       <c r="K13" s="25"/>
@@ -2963,27 +2963,27 @@
       <c r="AM13" s="30"/>
     </row>
     <row r="14" spans="2:39" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="66" t="s">
+      <c r="B14" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="67" t="s">
+      <c r="C14" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="67" t="s">
+      <c r="D14" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="68">
+      <c r="E14" s="41">
         <v>44253</v>
       </c>
-      <c r="F14" s="68">
+      <c r="F14" s="41">
         <v>44617</v>
       </c>
-      <c r="G14" s="42" t="s">
+      <c r="G14" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="65" t="s">
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="38" t="s">
         <v>29</v>
       </c>
       <c r="K14" s="25"/>
@@ -3015,27 +3015,27 @@
       <c r="AM14" s="30"/>
     </row>
     <row r="15" spans="2:39" s="28" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="66" t="s">
+      <c r="B15" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="67" t="s">
+      <c r="C15" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="67" t="s">
+      <c r="D15" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="68">
+      <c r="E15" s="41">
         <v>44647</v>
       </c>
-      <c r="F15" s="68">
+      <c r="F15" s="41">
         <v>45347</v>
       </c>
-      <c r="G15" s="42" t="s">
+      <c r="G15" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="65" t="s">
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="38" t="s">
         <v>36</v>
       </c>
       <c r="K15" s="25"/>
@@ -3072,9 +3072,9 @@
       <c r="D16" s="23"/>
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="40"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="62"/>
       <c r="J16" s="16"/>
       <c r="K16" s="25"/>
       <c r="L16" s="37"/>
@@ -3110,9 +3110,9 @@
       <c r="D17" s="23"/>
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="40"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="62"/>
       <c r="J17" s="16"/>
       <c r="K17" s="25"/>
       <c r="L17" s="37"/>
@@ -3148,9 +3148,9 @@
       <c r="D18" s="23"/>
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="40"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="62"/>
       <c r="J18" s="16"/>
       <c r="K18" s="25"/>
       <c r="L18" s="37"/>
@@ -3186,9 +3186,9 @@
       <c r="D19" s="23"/>
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="40"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="62"/>
       <c r="J19" s="16"/>
       <c r="K19" s="25"/>
       <c r="L19" s="37"/>
@@ -3224,9 +3224,9 @@
       <c r="D20" s="23"/>
       <c r="E20" s="24"/>
       <c r="F20" s="24"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="40"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="62"/>
       <c r="J20" s="16"/>
       <c r="K20" s="25"/>
       <c r="L20" s="37"/>
@@ -3262,9 +3262,9 @@
       <c r="D21" s="23"/>
       <c r="E21" s="24"/>
       <c r="F21" s="24"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="40"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="62"/>
       <c r="J21" s="16"/>
       <c r="K21" s="25"/>
       <c r="L21" s="37"/>
@@ -3300,9 +3300,9 @@
       <c r="D22" s="23"/>
       <c r="E22" s="24"/>
       <c r="F22" s="24"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="40"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="62"/>
       <c r="J22" s="16"/>
       <c r="K22" s="25"/>
       <c r="L22" s="37"/>
@@ -3338,9 +3338,9 @@
       <c r="D23" s="23"/>
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="40"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="62"/>
       <c r="J23" s="16"/>
       <c r="K23" s="25"/>
       <c r="L23" s="37"/>
@@ -3376,9 +3376,9 @@
       <c r="D24" s="23"/>
       <c r="E24" s="24"/>
       <c r="F24" s="24"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="40"/>
+      <c r="G24" s="60"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="62"/>
       <c r="J24" s="16"/>
       <c r="K24" s="25"/>
       <c r="L24" s="37"/>
@@ -3414,9 +3414,9 @@
       <c r="D25" s="23"/>
       <c r="E25" s="24"/>
       <c r="F25" s="24"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="40"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="62"/>
       <c r="J25" s="16"/>
       <c r="K25" s="25"/>
       <c r="L25" s="37"/>
@@ -3452,9 +3452,9 @@
       <c r="D26" s="23"/>
       <c r="E26" s="24"/>
       <c r="F26" s="24"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="40"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="62"/>
       <c r="J26" s="16"/>
       <c r="K26" s="25"/>
       <c r="L26" s="37"/>
@@ -3490,9 +3490,9 @@
       <c r="D27" s="23"/>
       <c r="E27" s="24"/>
       <c r="F27" s="24"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="40"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="62"/>
       <c r="J27" s="16"/>
       <c r="K27" s="25"/>
       <c r="L27" s="37"/>
@@ -3523,17 +3523,17 @@
       <c r="AM27" s="30"/>
     </row>
     <row r="28" spans="2:39" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B28" s="61" t="s">
+      <c r="B28" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="62"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="63"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="58"/>
       <c r="K28" s="15"/>
       <c r="L28" s="15"/>
       <c r="O28" s="6"/>
@@ -3563,17 +3563,17 @@
       <c r="AM28" s="4"/>
     </row>
     <row r="29" spans="2:39" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="61" t="s">
+      <c r="B29" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="62"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="63"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="58"/>
       <c r="K29" s="21"/>
       <c r="L29" s="21"/>
       <c r="N29" s="10"/>
@@ -3604,19 +3604,19 @@
       <c r="AM29" s="4"/>
     </row>
     <row r="30" spans="2:39" s="1" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="53" t="s">
+      <c r="B30" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="55"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="56"/>
-      <c r="J30" s="56"/>
-      <c r="K30" s="56"/>
-      <c r="L30" s="57"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="51"/>
+      <c r="K30" s="51"/>
+      <c r="L30" s="52"/>
       <c r="N30" s="11"/>
       <c r="O30" s="12"/>
       <c r="P30" s="2"/>
@@ -3645,17 +3645,17 @@
       <c r="AM30" s="4"/>
     </row>
     <row r="31" spans="2:39" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="54"/>
-      <c r="C31" s="58"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="59"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="59"/>
-      <c r="H31" s="59"/>
-      <c r="I31" s="59"/>
-      <c r="J31" s="59"/>
-      <c r="K31" s="59"/>
-      <c r="L31" s="60"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="54"/>
+      <c r="J31" s="54"/>
+      <c r="K31" s="54"/>
+      <c r="L31" s="55"/>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
       <c r="Q31" s="2"/>
@@ -3687,26 +3687,21 @@
     <protectedRange password="C71F" sqref="O11:Z29" name="Aralık1_1"/>
   </protectedRanges>
   <mergeCells count="51">
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="X12:Z12"/>
+    <mergeCell ref="O12:Q12"/>
+    <mergeCell ref="T12:V12"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="C30:L31"/>
     <mergeCell ref="B11:L11"/>
@@ -3718,26 +3713,31 @@
     <mergeCell ref="G13:I13"/>
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="G15:I15"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="X12:Z12"/>
-    <mergeCell ref="O12:Q12"/>
-    <mergeCell ref="T12:V12"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="C10:D10"/>
     <mergeCell ref="G27:I27"/>
     <mergeCell ref="G26:I26"/>
     <mergeCell ref="G25:I25"/>
     <mergeCell ref="G24:I24"/>
     <mergeCell ref="G23:I23"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="I8:J8"/>
   </mergeCells>
   <conditionalFormatting sqref="J12:K12 K16">
     <cfRule type="cellIs" dxfId="143" priority="247" operator="equal">

--- a/docs/cikti_taslagi_dolu.xlsx
+++ b/docs/cikti_taslagi_dolu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muhammed.bulut\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C23DA0E-9981-426E-82F0-43FDDE623E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFF0B96-EBEB-4926-A58A-357F0B2DA01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
     <definedName name="ilanNo">#REF!</definedName>
     <definedName name="MTarihi">#REF!</definedName>
     <definedName name="Muhammed_Taha_Kayaoğlu">[1]AG!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Karar Tutanağı'!$B$2:$L$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Karar Tutanağı'!$B$2:$L$32</definedName>
     <definedName name="YIL">[2]Adaylar!$CE$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="46">
   <si>
     <t xml:space="preserve">AD SOYAD </t>
   </si>
@@ -125,9 +125,6 @@
     <t>BRÜT ÜCRET (TL)</t>
   </si>
   <si>
-    <t>Toplam</t>
-  </si>
-  <si>
     <t>4a</t>
   </si>
   <si>
@@ -183,6 +180,15 @@
   </si>
   <si>
     <t>Tezsiz Yüksek Lisans</t>
+  </si>
+  <si>
+    <t>Toplam Prim Gün Sayısı</t>
+  </si>
+  <si>
+    <t>Yıl Gün Ay</t>
+  </si>
+  <si>
+    <t>DK Aralığı</t>
   </si>
 </sst>
 </file>
@@ -619,86 +625,86 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2483,7 +2489,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AM31"/>
+  <dimension ref="B1:AM32"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.44140625" customWidth="1"/>
@@ -2521,13 +2527,13 @@
       <c r="G2" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="65"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="56"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
@@ -2548,11 +2554,11 @@
       <c r="E3" s="19"/>
       <c r="F3" s="34"/>
       <c r="G3" s="35"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="68"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="59"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
@@ -2567,19 +2573,19 @@
       <c r="Z3" s="2"/>
     </row>
     <row r="4" spans="2:39" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
@@ -2598,24 +2604,24 @@
     </row>
     <row r="5" spans="2:39" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="17"/>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47" t="s">
+      <c r="D5" s="61"/>
+      <c r="E5" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47" t="s">
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="47"/>
-      <c r="K5" s="47" t="s">
+      <c r="J5" s="61"/>
+      <c r="K5" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="L5" s="47"/>
+      <c r="L5" s="61"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
@@ -2634,26 +2640,26 @@
     </row>
     <row r="6" spans="2:39" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="D6" s="63"/>
+      <c r="E6" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="43"/>
-      <c r="E6" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="45">
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="66">
         <v>43881</v>
       </c>
-      <c r="J6" s="45"/>
-      <c r="K6" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" s="43"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" s="63"/>
       <c r="O6" s="13"/>
       <c r="P6" s="13"/>
       <c r="Q6" s="13"/>
@@ -2672,26 +2678,26 @@
     </row>
     <row r="7" spans="2:39" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="43" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="43"/>
-      <c r="E7" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="45">
+      <c r="D7" s="63"/>
+      <c r="E7" s="65" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="66">
         <v>44247</v>
       </c>
-      <c r="J7" s="45"/>
-      <c r="K7" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7" s="43"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" s="63"/>
       <c r="O7" s="13"/>
       <c r="P7" s="13"/>
       <c r="Q7" s="13"/>
@@ -2710,26 +2716,26 @@
     </row>
     <row r="8" spans="2:39" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="42" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="63"/>
+      <c r="E8" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="43"/>
-      <c r="E8" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="45">
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="66">
         <v>46073</v>
       </c>
-      <c r="J8" s="45"/>
-      <c r="K8" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8" s="46"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" s="62"/>
       <c r="O8" s="13"/>
       <c r="P8" s="13"/>
       <c r="Q8" s="13"/>
@@ -2748,26 +2754,26 @@
     </row>
     <row r="9" spans="2:39" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="63" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="63"/>
+      <c r="E9" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="43"/>
-      <c r="E9" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="45">
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="66">
         <v>47169</v>
       </c>
-      <c r="J9" s="45"/>
-      <c r="K9" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" s="43"/>
+      <c r="J9" s="66"/>
+      <c r="K9" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" s="63"/>
       <c r="O9" s="13"/>
       <c r="P9" s="13"/>
       <c r="Q9" s="13"/>
@@ -2786,26 +2792,26 @@
     </row>
     <row r="10" spans="2:39" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="63" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="63"/>
+      <c r="E10" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="43"/>
-      <c r="E10" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="45">
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="66">
         <v>48264</v>
       </c>
-      <c r="J10" s="45"/>
-      <c r="K10" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="L10" s="46"/>
+      <c r="J10" s="66"/>
+      <c r="K10" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="L10" s="62"/>
       <c r="O10" s="13"/>
       <c r="P10" s="13"/>
       <c r="Q10" s="13"/>
@@ -2823,21 +2829,21 @@
       <c r="AC10" s="2"/>
     </row>
     <row r="11" spans="2:39" s="1" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47" t="s">
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="47"/>
-      <c r="K11" s="47"/>
-      <c r="L11" s="47"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="61"/>
+      <c r="K11" s="61"/>
+      <c r="L11" s="61"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
@@ -2870,11 +2876,11 @@
       <c r="F12" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="59" t="s">
+      <c r="G12" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
       <c r="J12" s="14" t="s">
         <v>12</v>
       </c>
@@ -2884,18 +2890,18 @@
       <c r="L12" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="O12" s="69"/>
-      <c r="P12" s="69"/>
-      <c r="Q12" s="69"/>
+      <c r="O12" s="60"/>
+      <c r="P12" s="60"/>
+      <c r="Q12" s="60"/>
       <c r="R12" s="36"/>
       <c r="S12" s="5"/>
-      <c r="T12" s="69"/>
-      <c r="U12" s="69"/>
-      <c r="V12" s="69"/>
+      <c r="T12" s="60"/>
+      <c r="U12" s="60"/>
+      <c r="V12" s="60"/>
       <c r="W12" s="5"/>
-      <c r="X12" s="69"/>
-      <c r="Y12" s="69"/>
-      <c r="Z12" s="69"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="60"/>
+      <c r="Z12" s="60"/>
       <c r="AA12" s="2"/>
       <c r="AB12" s="2"/>
       <c r="AC12" s="2"/>
@@ -2912,13 +2918,13 @@
     </row>
     <row r="13" spans="2:39" s="28" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="D13" s="40" t="s">
         <v>26</v>
-      </c>
-      <c r="D13" s="40" t="s">
-        <v>27</v>
       </c>
       <c r="E13" s="41">
         <v>43881</v>
@@ -2926,13 +2932,13 @@
       <c r="F13" s="41">
         <v>44252</v>
       </c>
-      <c r="G13" s="43" t="s">
+      <c r="G13" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="38" t="s">
         <v>28</v>
-      </c>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="38" t="s">
-        <v>29</v>
       </c>
       <c r="K13" s="25"/>
       <c r="L13" s="37"/>
@@ -2964,13 +2970,13 @@
     </row>
     <row r="14" spans="2:39" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="D14" s="40" t="s">
         <v>31</v>
-      </c>
-      <c r="D14" s="40" t="s">
-        <v>32</v>
       </c>
       <c r="E14" s="41">
         <v>44253</v>
@@ -2978,13 +2984,13 @@
       <c r="F14" s="41">
         <v>44617</v>
       </c>
-      <c r="G14" s="43" t="s">
+      <c r="G14" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="63"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="38" t="s">
         <v>28</v>
-      </c>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="38" t="s">
-        <v>29</v>
       </c>
       <c r="K14" s="25"/>
       <c r="L14" s="37"/>
@@ -3016,13 +3022,13 @@
     </row>
     <row r="15" spans="2:39" s="28" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="D15" s="40" t="s">
         <v>34</v>
-      </c>
-      <c r="D15" s="40" t="s">
-        <v>35</v>
       </c>
       <c r="E15" s="41">
         <v>44647</v>
@@ -3030,13 +3036,13 @@
       <c r="F15" s="41">
         <v>45347</v>
       </c>
-      <c r="G15" s="43" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
+      <c r="G15" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="63"/>
+      <c r="I15" s="63"/>
       <c r="J15" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K15" s="25"/>
       <c r="L15" s="37"/>
@@ -3072,9 +3078,9 @@
       <c r="D16" s="23"/>
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="62"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="53"/>
       <c r="J16" s="16"/>
       <c r="K16" s="25"/>
       <c r="L16" s="37"/>
@@ -3110,9 +3116,9 @@
       <c r="D17" s="23"/>
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="61"/>
-      <c r="I17" s="62"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="53"/>
       <c r="J17" s="16"/>
       <c r="K17" s="25"/>
       <c r="L17" s="37"/>
@@ -3148,9 +3154,9 @@
       <c r="D18" s="23"/>
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="62"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="53"/>
       <c r="J18" s="16"/>
       <c r="K18" s="25"/>
       <c r="L18" s="37"/>
@@ -3186,9 +3192,9 @@
       <c r="D19" s="23"/>
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="62"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="53"/>
       <c r="J19" s="16"/>
       <c r="K19" s="25"/>
       <c r="L19" s="37"/>
@@ -3224,9 +3230,9 @@
       <c r="D20" s="23"/>
       <c r="E20" s="24"/>
       <c r="F20" s="24"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="62"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="53"/>
       <c r="J20" s="16"/>
       <c r="K20" s="25"/>
       <c r="L20" s="37"/>
@@ -3262,9 +3268,9 @@
       <c r="D21" s="23"/>
       <c r="E21" s="24"/>
       <c r="F21" s="24"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="62"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="53"/>
       <c r="J21" s="16"/>
       <c r="K21" s="25"/>
       <c r="L21" s="37"/>
@@ -3300,9 +3306,9 @@
       <c r="D22" s="23"/>
       <c r="E22" s="24"/>
       <c r="F22" s="24"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="62"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="53"/>
       <c r="J22" s="16"/>
       <c r="K22" s="25"/>
       <c r="L22" s="37"/>
@@ -3338,9 +3344,9 @@
       <c r="D23" s="23"/>
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="62"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="53"/>
       <c r="J23" s="16"/>
       <c r="K23" s="25"/>
       <c r="L23" s="37"/>
@@ -3376,9 +3382,9 @@
       <c r="D24" s="23"/>
       <c r="E24" s="24"/>
       <c r="F24" s="24"/>
-      <c r="G24" s="60"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="62"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="53"/>
       <c r="J24" s="16"/>
       <c r="K24" s="25"/>
       <c r="L24" s="37"/>
@@ -3414,9 +3420,9 @@
       <c r="D25" s="23"/>
       <c r="E25" s="24"/>
       <c r="F25" s="24"/>
-      <c r="G25" s="60"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="62"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="53"/>
       <c r="J25" s="16"/>
       <c r="K25" s="25"/>
       <c r="L25" s="37"/>
@@ -3452,9 +3458,9 @@
       <c r="D26" s="23"/>
       <c r="E26" s="24"/>
       <c r="F26" s="24"/>
-      <c r="G26" s="60"/>
-      <c r="H26" s="61"/>
-      <c r="I26" s="62"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="53"/>
       <c r="J26" s="16"/>
       <c r="K26" s="25"/>
       <c r="L26" s="37"/>
@@ -3490,9 +3496,9 @@
       <c r="D27" s="23"/>
       <c r="E27" s="24"/>
       <c r="F27" s="24"/>
-      <c r="G27" s="60"/>
-      <c r="H27" s="61"/>
-      <c r="I27" s="62"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="53"/>
       <c r="J27" s="16"/>
       <c r="K27" s="25"/>
       <c r="L27" s="37"/>
@@ -3523,17 +3529,17 @@
       <c r="AM27" s="30"/>
     </row>
     <row r="28" spans="2:39" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B28" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="58"/>
+      <c r="B28" s="67" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="69"/>
       <c r="K28" s="15"/>
       <c r="L28" s="15"/>
       <c r="O28" s="6"/>
@@ -3563,17 +3569,17 @@
       <c r="AM28" s="4"/>
     </row>
     <row r="29" spans="2:39" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="58"/>
+      <c r="B29" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="69"/>
       <c r="K29" s="21"/>
       <c r="L29" s="21"/>
       <c r="N29" s="10"/>
@@ -3604,19 +3610,19 @@
       <c r="AM29" s="4"/>
     </row>
     <row r="30" spans="2:39" s="1" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="48" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="50"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="51"/>
-      <c r="K30" s="51"/>
-      <c r="L30" s="52"/>
+      <c r="B30" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="68"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="68"/>
+      <c r="F30" s="68"/>
+      <c r="G30" s="68"/>
+      <c r="H30" s="68"/>
+      <c r="I30" s="68"/>
+      <c r="J30" s="69"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
       <c r="N30" s="11"/>
       <c r="O30" s="12"/>
       <c r="P30" s="2"/>
@@ -3645,17 +3651,19 @@
       <c r="AM30" s="4"/>
     </row>
     <row r="31" spans="2:39" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="49"/>
-      <c r="C31" s="53"/>
-      <c r="D31" s="54"/>
-      <c r="E31" s="54"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="54"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="54"/>
-      <c r="J31" s="54"/>
-      <c r="K31" s="54"/>
-      <c r="L31" s="55"/>
+      <c r="B31" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="45"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="46"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="47"/>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
       <c r="Q31" s="2"/>
@@ -3682,28 +3690,39 @@
       <c r="AL31" s="4"/>
       <c r="AM31" s="4"/>
     </row>
+    <row r="32" spans="2:39" x14ac:dyDescent="0.3">
+      <c r="B32" s="44"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="49"/>
+      <c r="E32" s="49"/>
+      <c r="F32" s="49"/>
+      <c r="G32" s="49"/>
+      <c r="H32" s="49"/>
+      <c r="I32" s="49"/>
+      <c r="J32" s="49"/>
+      <c r="K32" s="49"/>
+      <c r="L32" s="50"/>
+    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange password="C71F" sqref="O11:Z29" name="Aralık1_1"/>
   </protectedRanges>
-  <mergeCells count="51">
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="X12:Z12"/>
-    <mergeCell ref="O12:Q12"/>
-    <mergeCell ref="T12:V12"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:L31"/>
+  <mergeCells count="50">
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:H8"/>
     <mergeCell ref="B11:L11"/>
     <mergeCell ref="B28:J28"/>
     <mergeCell ref="G12:I12"/>
@@ -3718,26 +3737,27 @@
     <mergeCell ref="G25:I25"/>
     <mergeCell ref="G24:I24"/>
     <mergeCell ref="G23:I23"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="X12:Z12"/>
+    <mergeCell ref="O12:Q12"/>
+    <mergeCell ref="T12:V12"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G18:I18"/>
   </mergeCells>
   <conditionalFormatting sqref="J12:K12 K16">
     <cfRule type="cellIs" dxfId="143" priority="247" operator="equal">

--- a/docs/cikti_taslagi_dolu.xlsx
+++ b/docs/cikti_taslagi_dolu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muhammed.bulut\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFF0B96-EBEB-4926-A58A-357F0B2DA01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32791E8-AD70-4133-9A40-C49011CCB69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -496,7 +496,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -519,9 +519,6 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -649,6 +646,33 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -679,32 +703,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2509,31 +2513,31 @@
   <sheetData>
     <row r="1" spans="2:39" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:39" s="1" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="33" t="s">
+      <c r="G2" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="54" t="s">
+      <c r="H2" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="56"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="64"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
@@ -2548,17 +2552,17 @@
       <c r="Z2" s="2"/>
     </row>
     <row r="3" spans="2:39" s="1" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-      <c r="L3" s="59"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="67"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
@@ -2573,19 +2577,19 @@
       <c r="Z3" s="2"/>
     </row>
     <row r="4" spans="2:39" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
@@ -2603,25 +2607,25 @@
       <c r="AC4" s="2"/>
     </row>
     <row r="5" spans="2:39" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="17"/>
-      <c r="C5" s="61" t="s">
+      <c r="B5" s="16"/>
+      <c r="C5" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61" t="s">
+      <c r="D5" s="57"/>
+      <c r="E5" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61" t="s">
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61" t="s">
+      <c r="J5" s="57"/>
+      <c r="K5" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="L5" s="61"/>
+      <c r="L5" s="57"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
@@ -2639,211 +2643,211 @@
       <c r="AC5" s="2"/>
     </row>
     <row r="6" spans="2:39" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="63" t="s">
+      <c r="C6" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="63"/>
-      <c r="E6" s="65" t="s">
+      <c r="D6" s="54"/>
+      <c r="E6" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63"/>
-      <c r="I6" s="66">
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="55">
         <v>43881</v>
       </c>
-      <c r="J6" s="66"/>
-      <c r="K6" s="63" t="s">
+      <c r="J6" s="55"/>
+      <c r="K6" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="L6" s="63"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
+      <c r="L6" s="54"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="12"/>
+      <c r="Y6" s="12"/>
+      <c r="Z6" s="12"/>
       <c r="AA6" s="2"/>
       <c r="AB6" s="2"/>
       <c r="AC6" s="2"/>
     </row>
     <row r="7" spans="2:39" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="63" t="s">
+      <c r="C7" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="63"/>
-      <c r="E7" s="65" t="s">
+      <c r="D7" s="54"/>
+      <c r="E7" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="66">
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="55">
         <v>44247</v>
       </c>
-      <c r="J7" s="66"/>
-      <c r="K7" s="63" t="s">
+      <c r="J7" s="55"/>
+      <c r="K7" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="63"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="13"/>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="13"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13"/>
+      <c r="L7" s="54"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
+      <c r="V7" s="12"/>
+      <c r="W7" s="12"/>
+      <c r="X7" s="12"/>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="12"/>
       <c r="AA7" s="2"/>
       <c r="AB7" s="2"/>
       <c r="AC7" s="2"/>
     </row>
     <row r="8" spans="2:39" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="63" t="s">
+      <c r="C8" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="63"/>
-      <c r="E8" s="65" t="s">
+      <c r="D8" s="54"/>
+      <c r="E8" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="66">
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="55">
         <v>46073</v>
       </c>
-      <c r="J8" s="66"/>
-      <c r="K8" s="62" t="s">
+      <c r="J8" s="55"/>
+      <c r="K8" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="L8" s="62"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="13"/>
-      <c r="U8" s="13"/>
-      <c r="V8" s="13"/>
-      <c r="W8" s="13"/>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="13"/>
-      <c r="Z8" s="13"/>
+      <c r="L8" s="56"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="12"/>
+      <c r="V8" s="12"/>
+      <c r="W8" s="12"/>
+      <c r="X8" s="12"/>
+      <c r="Y8" s="12"/>
+      <c r="Z8" s="12"/>
       <c r="AA8" s="2"/>
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
     </row>
     <row r="9" spans="2:39" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="63" t="s">
+      <c r="C9" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="63"/>
-      <c r="E9" s="65" t="s">
+      <c r="D9" s="54"/>
+      <c r="E9" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="66">
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="55">
         <v>47169</v>
       </c>
-      <c r="J9" s="66"/>
-      <c r="K9" s="63" t="s">
+      <c r="J9" s="55"/>
+      <c r="K9" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="L9" s="63"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="13"/>
-      <c r="U9" s="13"/>
-      <c r="V9" s="13"/>
-      <c r="W9" s="13"/>
-      <c r="X9" s="13"/>
-      <c r="Y9" s="13"/>
-      <c r="Z9" s="13"/>
+      <c r="L9" s="54"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="12"/>
+      <c r="V9" s="12"/>
+      <c r="W9" s="12"/>
+      <c r="X9" s="12"/>
+      <c r="Y9" s="12"/>
+      <c r="Z9" s="12"/>
       <c r="AA9" s="2"/>
       <c r="AB9" s="2"/>
       <c r="AC9" s="2"/>
     </row>
     <row r="10" spans="2:39" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="63" t="s">
+      <c r="C10" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="63"/>
-      <c r="E10" s="65" t="s">
+      <c r="D10" s="54"/>
+      <c r="E10" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="66">
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="55">
         <v>48264</v>
       </c>
-      <c r="J10" s="66"/>
-      <c r="K10" s="62" t="s">
+      <c r="J10" s="55"/>
+      <c r="K10" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="L10" s="62"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="S10" s="13"/>
-      <c r="T10" s="13"/>
-      <c r="U10" s="13"/>
-      <c r="V10" s="13"/>
-      <c r="W10" s="13"/>
-      <c r="X10" s="13"/>
-      <c r="Y10" s="13"/>
-      <c r="Z10" s="13"/>
+      <c r="L10" s="56"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="12"/>
+      <c r="V10" s="12"/>
+      <c r="W10" s="12"/>
+      <c r="X10" s="12"/>
+      <c r="Y10" s="12"/>
+      <c r="Z10" s="12"/>
       <c r="AA10" s="2"/>
       <c r="AB10" s="2"/>
       <c r="AC10" s="2"/>
     </row>
     <row r="11" spans="2:39" s="1" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="61" t="s">
+      <c r="B11" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61" t="s">
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
-      <c r="L11" s="61"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="57"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
@@ -2861,47 +2865,47 @@
       <c r="AC11" s="2"/>
     </row>
     <row r="12" spans="2:39" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="64" t="s">
+      <c r="G12" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="14" t="s">
+      <c r="H12" s="58"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="K12" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="L12" s="14" t="s">
+      <c r="L12" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="O12" s="60"/>
-      <c r="P12" s="60"/>
-      <c r="Q12" s="60"/>
-      <c r="R12" s="36"/>
+      <c r="O12" s="68"/>
+      <c r="P12" s="68"/>
+      <c r="Q12" s="68"/>
+      <c r="R12" s="35"/>
       <c r="S12" s="5"/>
-      <c r="T12" s="60"/>
-      <c r="U12" s="60"/>
-      <c r="V12" s="60"/>
+      <c r="T12" s="68"/>
+      <c r="U12" s="68"/>
+      <c r="V12" s="68"/>
       <c r="W12" s="5"/>
-      <c r="X12" s="60"/>
-      <c r="Y12" s="60"/>
-      <c r="Z12" s="60"/>
+      <c r="X12" s="68"/>
+      <c r="Y12" s="68"/>
+      <c r="Z12" s="68"/>
       <c r="AA12" s="2"/>
       <c r="AB12" s="2"/>
       <c r="AC12" s="2"/>
@@ -2916,632 +2920,632 @@
       <c r="AL12" s="4"/>
       <c r="AM12" s="4"/>
     </row>
-    <row r="13" spans="2:39" s="28" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="39" t="s">
+    <row r="13" spans="2:39" s="27" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="40" t="s">
+      <c r="D13" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="40">
         <v>43881</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="40">
         <v>44252</v>
       </c>
-      <c r="G13" s="63" t="s">
+      <c r="G13" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="H13" s="63"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="38" t="s">
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="K13" s="25"/>
-      <c r="L13" s="37"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
-      <c r="Q13" s="27"/>
-      <c r="R13" s="27"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="36"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="26"/>
+      <c r="Q13" s="26"/>
+      <c r="R13" s="26"/>
       <c r="S13" s="5"/>
-      <c r="T13" s="27"/>
-      <c r="U13" s="27"/>
-      <c r="V13" s="27"/>
+      <c r="T13" s="26"/>
+      <c r="U13" s="26"/>
+      <c r="V13" s="26"/>
       <c r="W13" s="5"/>
-      <c r="X13" s="27"/>
-      <c r="Y13" s="27"/>
-      <c r="Z13" s="27"/>
-      <c r="AA13" s="29"/>
-      <c r="AB13" s="29"/>
-      <c r="AC13" s="29"/>
-      <c r="AD13" s="30"/>
-      <c r="AE13" s="30"/>
-      <c r="AF13" s="30"/>
-      <c r="AG13" s="30"/>
-      <c r="AH13" s="30"/>
-      <c r="AI13" s="30"/>
-      <c r="AJ13" s="30"/>
-      <c r="AK13" s="30"/>
-      <c r="AL13" s="30"/>
-      <c r="AM13" s="30"/>
+      <c r="X13" s="26"/>
+      <c r="Y13" s="26"/>
+      <c r="Z13" s="26"/>
+      <c r="AA13" s="28"/>
+      <c r="AB13" s="28"/>
+      <c r="AC13" s="28"/>
+      <c r="AD13" s="29"/>
+      <c r="AE13" s="29"/>
+      <c r="AF13" s="29"/>
+      <c r="AG13" s="29"/>
+      <c r="AH13" s="29"/>
+      <c r="AI13" s="29"/>
+      <c r="AJ13" s="29"/>
+      <c r="AK13" s="29"/>
+      <c r="AL13" s="29"/>
+      <c r="AM13" s="29"/>
     </row>
-    <row r="14" spans="2:39" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="39" t="s">
+    <row r="14" spans="2:39" s="27" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="40" t="s">
+      <c r="D14" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="40">
         <v>44253</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="40">
         <v>44617</v>
       </c>
-      <c r="G14" s="63" t="s">
+      <c r="G14" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="H14" s="63"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="38" t="s">
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="K14" s="25"/>
-      <c r="L14" s="37"/>
-      <c r="O14" s="27"/>
-      <c r="P14" s="27"/>
-      <c r="Q14" s="27"/>
-      <c r="R14" s="27"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="36"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="26"/>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="26"/>
       <c r="S14" s="5"/>
-      <c r="T14" s="27"/>
-      <c r="U14" s="27"/>
-      <c r="V14" s="27"/>
+      <c r="T14" s="26"/>
+      <c r="U14" s="26"/>
+      <c r="V14" s="26"/>
       <c r="W14" s="5"/>
-      <c r="X14" s="27"/>
-      <c r="Y14" s="27"/>
-      <c r="Z14" s="27"/>
-      <c r="AA14" s="29"/>
-      <c r="AB14" s="29"/>
-      <c r="AC14" s="29"/>
-      <c r="AD14" s="30"/>
-      <c r="AE14" s="30"/>
-      <c r="AF14" s="30"/>
-      <c r="AG14" s="30"/>
-      <c r="AH14" s="30"/>
-      <c r="AI14" s="30"/>
-      <c r="AJ14" s="30"/>
-      <c r="AK14" s="30"/>
-      <c r="AL14" s="30"/>
-      <c r="AM14" s="30"/>
+      <c r="X14" s="26"/>
+      <c r="Y14" s="26"/>
+      <c r="Z14" s="26"/>
+      <c r="AA14" s="28"/>
+      <c r="AB14" s="28"/>
+      <c r="AC14" s="28"/>
+      <c r="AD14" s="29"/>
+      <c r="AE14" s="29"/>
+      <c r="AF14" s="29"/>
+      <c r="AG14" s="29"/>
+      <c r="AH14" s="29"/>
+      <c r="AI14" s="29"/>
+      <c r="AJ14" s="29"/>
+      <c r="AK14" s="29"/>
+      <c r="AL14" s="29"/>
+      <c r="AM14" s="29"/>
     </row>
-    <row r="15" spans="2:39" s="28" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="39" t="s">
+    <row r="15" spans="2:39" s="27" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="40" t="s">
+      <c r="D15" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="40">
         <v>44647</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="40">
         <v>45347</v>
       </c>
-      <c r="G15" s="63" t="s">
+      <c r="G15" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="H15" s="63"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="38" t="s">
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K15" s="25"/>
-      <c r="L15" s="37"/>
-      <c r="O15" s="27"/>
-      <c r="P15" s="27"/>
-      <c r="Q15" s="27"/>
-      <c r="R15" s="27"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="36"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="26"/>
+      <c r="Q15" s="26"/>
+      <c r="R15" s="26"/>
       <c r="S15" s="5"/>
-      <c r="T15" s="27"/>
-      <c r="U15" s="27"/>
-      <c r="V15" s="27"/>
+      <c r="T15" s="26"/>
+      <c r="U15" s="26"/>
+      <c r="V15" s="26"/>
       <c r="W15" s="5"/>
-      <c r="X15" s="27"/>
-      <c r="Y15" s="27"/>
-      <c r="Z15" s="27"/>
-      <c r="AA15" s="29"/>
-      <c r="AB15" s="29"/>
-      <c r="AC15" s="29"/>
-      <c r="AD15" s="30"/>
-      <c r="AE15" s="30"/>
-      <c r="AF15" s="30"/>
-      <c r="AG15" s="30"/>
-      <c r="AH15" s="30"/>
-      <c r="AI15" s="30"/>
-      <c r="AJ15" s="30"/>
-      <c r="AK15" s="30"/>
-      <c r="AL15" s="30"/>
-      <c r="AM15" s="30"/>
+      <c r="X15" s="26"/>
+      <c r="Y15" s="26"/>
+      <c r="Z15" s="26"/>
+      <c r="AA15" s="28"/>
+      <c r="AB15" s="28"/>
+      <c r="AC15" s="28"/>
+      <c r="AD15" s="29"/>
+      <c r="AE15" s="29"/>
+      <c r="AF15" s="29"/>
+      <c r="AG15" s="29"/>
+      <c r="AH15" s="29"/>
+      <c r="AI15" s="29"/>
+      <c r="AJ15" s="29"/>
+      <c r="AK15" s="29"/>
+      <c r="AL15" s="29"/>
+      <c r="AM15" s="29"/>
     </row>
-    <row r="16" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="22"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="53"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="37"/>
-      <c r="O16" s="26"/>
-      <c r="P16" s="26"/>
-      <c r="Q16" s="26"/>
-      <c r="R16" s="26"/>
+    <row r="16" spans="2:39" s="27" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="21"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="36"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="25"/>
       <c r="S16" s="5"/>
-      <c r="T16" s="26"/>
-      <c r="U16" s="26"/>
-      <c r="V16" s="26"/>
+      <c r="T16" s="25"/>
+      <c r="U16" s="25"/>
+      <c r="V16" s="25"/>
       <c r="W16" s="5"/>
-      <c r="X16" s="26"/>
-      <c r="Y16" s="26"/>
-      <c r="Z16" s="26"/>
-      <c r="AA16" s="29"/>
-      <c r="AB16" s="29"/>
-      <c r="AC16" s="29"/>
-      <c r="AD16" s="30"/>
-      <c r="AE16" s="30"/>
-      <c r="AF16" s="30"/>
-      <c r="AG16" s="30"/>
-      <c r="AH16" s="30"/>
-      <c r="AI16" s="30"/>
-      <c r="AJ16" s="30"/>
-      <c r="AK16" s="30"/>
-      <c r="AL16" s="30"/>
-      <c r="AM16" s="30"/>
+      <c r="X16" s="25"/>
+      <c r="Y16" s="25"/>
+      <c r="Z16" s="25"/>
+      <c r="AA16" s="28"/>
+      <c r="AB16" s="28"/>
+      <c r="AC16" s="28"/>
+      <c r="AD16" s="29"/>
+      <c r="AE16" s="29"/>
+      <c r="AF16" s="29"/>
+      <c r="AG16" s="29"/>
+      <c r="AH16" s="29"/>
+      <c r="AI16" s="29"/>
+      <c r="AJ16" s="29"/>
+      <c r="AK16" s="29"/>
+      <c r="AL16" s="29"/>
+      <c r="AM16" s="29"/>
     </row>
-    <row r="17" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="22"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="53"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="37"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="31"/>
-      <c r="Q17" s="31"/>
-      <c r="R17" s="31"/>
+    <row r="17" spans="2:39" s="27" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="21"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="36"/>
+      <c r="O17" s="30"/>
+      <c r="P17" s="30"/>
+      <c r="Q17" s="30"/>
+      <c r="R17" s="30"/>
       <c r="S17" s="5"/>
-      <c r="T17" s="31"/>
-      <c r="U17" s="31"/>
-      <c r="V17" s="31"/>
+      <c r="T17" s="30"/>
+      <c r="U17" s="30"/>
+      <c r="V17" s="30"/>
       <c r="W17" s="5"/>
-      <c r="X17" s="31"/>
-      <c r="Y17" s="31"/>
-      <c r="Z17" s="31"/>
-      <c r="AA17" s="29"/>
-      <c r="AB17" s="29"/>
-      <c r="AC17" s="29"/>
-      <c r="AD17" s="30"/>
-      <c r="AE17" s="30"/>
-      <c r="AF17" s="30"/>
-      <c r="AG17" s="30"/>
-      <c r="AH17" s="30"/>
-      <c r="AI17" s="30"/>
-      <c r="AJ17" s="30"/>
-      <c r="AK17" s="30"/>
-      <c r="AL17" s="30"/>
-      <c r="AM17" s="30"/>
+      <c r="X17" s="30"/>
+      <c r="Y17" s="30"/>
+      <c r="Z17" s="30"/>
+      <c r="AA17" s="28"/>
+      <c r="AB17" s="28"/>
+      <c r="AC17" s="28"/>
+      <c r="AD17" s="29"/>
+      <c r="AE17" s="29"/>
+      <c r="AF17" s="29"/>
+      <c r="AG17" s="29"/>
+      <c r="AH17" s="29"/>
+      <c r="AI17" s="29"/>
+      <c r="AJ17" s="29"/>
+      <c r="AK17" s="29"/>
+      <c r="AL17" s="29"/>
+      <c r="AM17" s="29"/>
     </row>
-    <row r="18" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="22"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="25"/>
-      <c r="L18" s="37"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
+    <row r="18" spans="2:39" s="27" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="21"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="36"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
       <c r="S18" s="5"/>
-      <c r="T18" s="36"/>
-      <c r="U18" s="36"/>
-      <c r="V18" s="36"/>
+      <c r="T18" s="35"/>
+      <c r="U18" s="35"/>
+      <c r="V18" s="35"/>
       <c r="W18" s="5"/>
-      <c r="X18" s="36"/>
-      <c r="Y18" s="36"/>
-      <c r="Z18" s="36"/>
-      <c r="AA18" s="29"/>
-      <c r="AB18" s="29"/>
-      <c r="AC18" s="29"/>
-      <c r="AD18" s="30"/>
-      <c r="AE18" s="30"/>
-      <c r="AF18" s="30"/>
-      <c r="AG18" s="30"/>
-      <c r="AH18" s="30"/>
-      <c r="AI18" s="30"/>
-      <c r="AJ18" s="30"/>
-      <c r="AK18" s="30"/>
-      <c r="AL18" s="30"/>
-      <c r="AM18" s="30"/>
+      <c r="X18" s="35"/>
+      <c r="Y18" s="35"/>
+      <c r="Z18" s="35"/>
+      <c r="AA18" s="28"/>
+      <c r="AB18" s="28"/>
+      <c r="AC18" s="28"/>
+      <c r="AD18" s="29"/>
+      <c r="AE18" s="29"/>
+      <c r="AF18" s="29"/>
+      <c r="AG18" s="29"/>
+      <c r="AH18" s="29"/>
+      <c r="AI18" s="29"/>
+      <c r="AJ18" s="29"/>
+      <c r="AK18" s="29"/>
+      <c r="AL18" s="29"/>
+      <c r="AM18" s="29"/>
     </row>
-    <row r="19" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="22"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="37"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
+    <row r="19" spans="2:39" s="27" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="21"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="36"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
       <c r="S19" s="5"/>
-      <c r="T19" s="36"/>
-      <c r="U19" s="36"/>
-      <c r="V19" s="36"/>
+      <c r="T19" s="35"/>
+      <c r="U19" s="35"/>
+      <c r="V19" s="35"/>
       <c r="W19" s="5"/>
-      <c r="X19" s="36"/>
-      <c r="Y19" s="36"/>
-      <c r="Z19" s="36"/>
-      <c r="AA19" s="29"/>
-      <c r="AB19" s="29"/>
-      <c r="AC19" s="29"/>
-      <c r="AD19" s="30"/>
-      <c r="AE19" s="30"/>
-      <c r="AF19" s="30"/>
-      <c r="AG19" s="30"/>
-      <c r="AH19" s="30"/>
-      <c r="AI19" s="30"/>
-      <c r="AJ19" s="30"/>
-      <c r="AK19" s="30"/>
-      <c r="AL19" s="30"/>
-      <c r="AM19" s="30"/>
+      <c r="X19" s="35"/>
+      <c r="Y19" s="35"/>
+      <c r="Z19" s="35"/>
+      <c r="AA19" s="28"/>
+      <c r="AB19" s="28"/>
+      <c r="AC19" s="28"/>
+      <c r="AD19" s="29"/>
+      <c r="AE19" s="29"/>
+      <c r="AF19" s="29"/>
+      <c r="AG19" s="29"/>
+      <c r="AH19" s="29"/>
+      <c r="AI19" s="29"/>
+      <c r="AJ19" s="29"/>
+      <c r="AK19" s="29"/>
+      <c r="AL19" s="29"/>
+      <c r="AM19" s="29"/>
     </row>
-    <row r="20" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="22"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="37"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
+    <row r="20" spans="2:39" s="27" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="21"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="36"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="35"/>
+      <c r="R20" s="35"/>
       <c r="S20" s="5"/>
-      <c r="T20" s="36"/>
-      <c r="U20" s="36"/>
-      <c r="V20" s="36"/>
+      <c r="T20" s="35"/>
+      <c r="U20" s="35"/>
+      <c r="V20" s="35"/>
       <c r="W20" s="5"/>
-      <c r="X20" s="36"/>
-      <c r="Y20" s="36"/>
-      <c r="Z20" s="36"/>
-      <c r="AA20" s="29"/>
-      <c r="AB20" s="29"/>
-      <c r="AC20" s="29"/>
-      <c r="AD20" s="30"/>
-      <c r="AE20" s="30"/>
-      <c r="AF20" s="30"/>
-      <c r="AG20" s="30"/>
-      <c r="AH20" s="30"/>
-      <c r="AI20" s="30"/>
-      <c r="AJ20" s="30"/>
-      <c r="AK20" s="30"/>
-      <c r="AL20" s="30"/>
-      <c r="AM20" s="30"/>
+      <c r="X20" s="35"/>
+      <c r="Y20" s="35"/>
+      <c r="Z20" s="35"/>
+      <c r="AA20" s="28"/>
+      <c r="AB20" s="28"/>
+      <c r="AC20" s="28"/>
+      <c r="AD20" s="29"/>
+      <c r="AE20" s="29"/>
+      <c r="AF20" s="29"/>
+      <c r="AG20" s="29"/>
+      <c r="AH20" s="29"/>
+      <c r="AI20" s="29"/>
+      <c r="AJ20" s="29"/>
+      <c r="AK20" s="29"/>
+      <c r="AL20" s="29"/>
+      <c r="AM20" s="29"/>
     </row>
-    <row r="21" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="22"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="25"/>
-      <c r="L21" s="37"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
+    <row r="21" spans="2:39" s="27" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="21"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="36"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="35"/>
+      <c r="Q21" s="35"/>
+      <c r="R21" s="35"/>
       <c r="S21" s="5"/>
-      <c r="T21" s="36"/>
-      <c r="U21" s="36"/>
-      <c r="V21" s="36"/>
+      <c r="T21" s="35"/>
+      <c r="U21" s="35"/>
+      <c r="V21" s="35"/>
       <c r="W21" s="5"/>
-      <c r="X21" s="36"/>
-      <c r="Y21" s="36"/>
-      <c r="Z21" s="36"/>
-      <c r="AA21" s="29"/>
-      <c r="AB21" s="29"/>
-      <c r="AC21" s="29"/>
-      <c r="AD21" s="30"/>
-      <c r="AE21" s="30"/>
-      <c r="AF21" s="30"/>
-      <c r="AG21" s="30"/>
-      <c r="AH21" s="30"/>
-      <c r="AI21" s="30"/>
-      <c r="AJ21" s="30"/>
-      <c r="AK21" s="30"/>
-      <c r="AL21" s="30"/>
-      <c r="AM21" s="30"/>
+      <c r="X21" s="35"/>
+      <c r="Y21" s="35"/>
+      <c r="Z21" s="35"/>
+      <c r="AA21" s="28"/>
+      <c r="AB21" s="28"/>
+      <c r="AC21" s="28"/>
+      <c r="AD21" s="29"/>
+      <c r="AE21" s="29"/>
+      <c r="AF21" s="29"/>
+      <c r="AG21" s="29"/>
+      <c r="AH21" s="29"/>
+      <c r="AI21" s="29"/>
+      <c r="AJ21" s="29"/>
+      <c r="AK21" s="29"/>
+      <c r="AL21" s="29"/>
+      <c r="AM21" s="29"/>
     </row>
-    <row r="22" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="22"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="37"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="36"/>
+    <row r="22" spans="2:39" s="27" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="21"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="36"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="35"/>
+      <c r="Q22" s="35"/>
+      <c r="R22" s="35"/>
       <c r="S22" s="5"/>
-      <c r="T22" s="36"/>
-      <c r="U22" s="36"/>
-      <c r="V22" s="36"/>
+      <c r="T22" s="35"/>
+      <c r="U22" s="35"/>
+      <c r="V22" s="35"/>
       <c r="W22" s="5"/>
-      <c r="X22" s="36"/>
-      <c r="Y22" s="36"/>
-      <c r="Z22" s="36"/>
-      <c r="AA22" s="29"/>
-      <c r="AB22" s="29"/>
-      <c r="AC22" s="29"/>
-      <c r="AD22" s="30"/>
-      <c r="AE22" s="30"/>
-      <c r="AF22" s="30"/>
-      <c r="AG22" s="30"/>
-      <c r="AH22" s="30"/>
-      <c r="AI22" s="30"/>
-      <c r="AJ22" s="30"/>
-      <c r="AK22" s="30"/>
-      <c r="AL22" s="30"/>
-      <c r="AM22" s="30"/>
+      <c r="X22" s="35"/>
+      <c r="Y22" s="35"/>
+      <c r="Z22" s="35"/>
+      <c r="AA22" s="28"/>
+      <c r="AB22" s="28"/>
+      <c r="AC22" s="28"/>
+      <c r="AD22" s="29"/>
+      <c r="AE22" s="29"/>
+      <c r="AF22" s="29"/>
+      <c r="AG22" s="29"/>
+      <c r="AH22" s="29"/>
+      <c r="AI22" s="29"/>
+      <c r="AJ22" s="29"/>
+      <c r="AK22" s="29"/>
+      <c r="AL22" s="29"/>
+      <c r="AM22" s="29"/>
     </row>
-    <row r="23" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="22"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="37"/>
-      <c r="O23" s="36"/>
-      <c r="P23" s="36"/>
-      <c r="Q23" s="36"/>
-      <c r="R23" s="36"/>
+    <row r="23" spans="2:39" s="27" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="21"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="36"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="35"/>
       <c r="S23" s="5"/>
-      <c r="T23" s="36"/>
-      <c r="U23" s="36"/>
-      <c r="V23" s="36"/>
+      <c r="T23" s="35"/>
+      <c r="U23" s="35"/>
+      <c r="V23" s="35"/>
       <c r="W23" s="5"/>
-      <c r="X23" s="36"/>
-      <c r="Y23" s="36"/>
-      <c r="Z23" s="36"/>
-      <c r="AA23" s="29"/>
-      <c r="AB23" s="29"/>
-      <c r="AC23" s="29"/>
-      <c r="AD23" s="30"/>
-      <c r="AE23" s="30"/>
-      <c r="AF23" s="30"/>
-      <c r="AG23" s="30"/>
-      <c r="AH23" s="30"/>
-      <c r="AI23" s="30"/>
-      <c r="AJ23" s="30"/>
-      <c r="AK23" s="30"/>
-      <c r="AL23" s="30"/>
-      <c r="AM23" s="30"/>
+      <c r="X23" s="35"/>
+      <c r="Y23" s="35"/>
+      <c r="Z23" s="35"/>
+      <c r="AA23" s="28"/>
+      <c r="AB23" s="28"/>
+      <c r="AC23" s="28"/>
+      <c r="AD23" s="29"/>
+      <c r="AE23" s="29"/>
+      <c r="AF23" s="29"/>
+      <c r="AG23" s="29"/>
+      <c r="AH23" s="29"/>
+      <c r="AI23" s="29"/>
+      <c r="AJ23" s="29"/>
+      <c r="AK23" s="29"/>
+      <c r="AL23" s="29"/>
+      <c r="AM23" s="29"/>
     </row>
-    <row r="24" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="22"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="37"/>
-      <c r="O24" s="36"/>
-      <c r="P24" s="36"/>
-      <c r="Q24" s="36"/>
-      <c r="R24" s="36"/>
+    <row r="24" spans="2:39" s="27" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="21"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="36"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="35"/>
+      <c r="Q24" s="35"/>
+      <c r="R24" s="35"/>
       <c r="S24" s="5"/>
-      <c r="T24" s="36"/>
-      <c r="U24" s="36"/>
-      <c r="V24" s="36"/>
+      <c r="T24" s="35"/>
+      <c r="U24" s="35"/>
+      <c r="V24" s="35"/>
       <c r="W24" s="5"/>
-      <c r="X24" s="36"/>
-      <c r="Y24" s="36"/>
-      <c r="Z24" s="36"/>
-      <c r="AA24" s="29"/>
-      <c r="AB24" s="29"/>
-      <c r="AC24" s="29"/>
-      <c r="AD24" s="30"/>
-      <c r="AE24" s="30"/>
-      <c r="AF24" s="30"/>
-      <c r="AG24" s="30"/>
-      <c r="AH24" s="30"/>
-      <c r="AI24" s="30"/>
-      <c r="AJ24" s="30"/>
-      <c r="AK24" s="30"/>
-      <c r="AL24" s="30"/>
-      <c r="AM24" s="30"/>
+      <c r="X24" s="35"/>
+      <c r="Y24" s="35"/>
+      <c r="Z24" s="35"/>
+      <c r="AA24" s="28"/>
+      <c r="AB24" s="28"/>
+      <c r="AC24" s="28"/>
+      <c r="AD24" s="29"/>
+      <c r="AE24" s="29"/>
+      <c r="AF24" s="29"/>
+      <c r="AG24" s="29"/>
+      <c r="AH24" s="29"/>
+      <c r="AI24" s="29"/>
+      <c r="AJ24" s="29"/>
+      <c r="AK24" s="29"/>
+      <c r="AL24" s="29"/>
+      <c r="AM24" s="29"/>
     </row>
-    <row r="25" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="22"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="53"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="37"/>
-      <c r="O25" s="36"/>
-      <c r="P25" s="36"/>
-      <c r="Q25" s="36"/>
-      <c r="R25" s="36"/>
+    <row r="25" spans="2:39" s="27" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="21"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="36"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="35"/>
+      <c r="Q25" s="35"/>
+      <c r="R25" s="35"/>
       <c r="S25" s="5"/>
-      <c r="T25" s="36"/>
-      <c r="U25" s="36"/>
-      <c r="V25" s="36"/>
+      <c r="T25" s="35"/>
+      <c r="U25" s="35"/>
+      <c r="V25" s="35"/>
       <c r="W25" s="5"/>
-      <c r="X25" s="36"/>
-      <c r="Y25" s="36"/>
-      <c r="Z25" s="36"/>
-      <c r="AA25" s="29"/>
-      <c r="AB25" s="29"/>
-      <c r="AC25" s="29"/>
-      <c r="AD25" s="30"/>
-      <c r="AE25" s="30"/>
-      <c r="AF25" s="30"/>
-      <c r="AG25" s="30"/>
-      <c r="AH25" s="30"/>
-      <c r="AI25" s="30"/>
-      <c r="AJ25" s="30"/>
-      <c r="AK25" s="30"/>
-      <c r="AL25" s="30"/>
-      <c r="AM25" s="30"/>
+      <c r="X25" s="35"/>
+      <c r="Y25" s="35"/>
+      <c r="Z25" s="35"/>
+      <c r="AA25" s="28"/>
+      <c r="AB25" s="28"/>
+      <c r="AC25" s="28"/>
+      <c r="AD25" s="29"/>
+      <c r="AE25" s="29"/>
+      <c r="AF25" s="29"/>
+      <c r="AG25" s="29"/>
+      <c r="AH25" s="29"/>
+      <c r="AI25" s="29"/>
+      <c r="AJ25" s="29"/>
+      <c r="AK25" s="29"/>
+      <c r="AL25" s="29"/>
+      <c r="AM25" s="29"/>
     </row>
-    <row r="26" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="22"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="25"/>
-      <c r="L26" s="37"/>
-      <c r="O26" s="36"/>
-      <c r="P26" s="36"/>
-      <c r="Q26" s="36"/>
-      <c r="R26" s="36"/>
+    <row r="26" spans="2:39" s="27" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="21"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="36"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="35"/>
+      <c r="Q26" s="35"/>
+      <c r="R26" s="35"/>
       <c r="S26" s="5"/>
-      <c r="T26" s="36"/>
-      <c r="U26" s="36"/>
-      <c r="V26" s="36"/>
+      <c r="T26" s="35"/>
+      <c r="U26" s="35"/>
+      <c r="V26" s="35"/>
       <c r="W26" s="5"/>
-      <c r="X26" s="36"/>
-      <c r="Y26" s="36"/>
-      <c r="Z26" s="36"/>
-      <c r="AA26" s="29"/>
-      <c r="AB26" s="29"/>
-      <c r="AC26" s="29"/>
-      <c r="AD26" s="30"/>
-      <c r="AE26" s="30"/>
-      <c r="AF26" s="30"/>
-      <c r="AG26" s="30"/>
-      <c r="AH26" s="30"/>
-      <c r="AI26" s="30"/>
-      <c r="AJ26" s="30"/>
-      <c r="AK26" s="30"/>
-      <c r="AL26" s="30"/>
-      <c r="AM26" s="30"/>
+      <c r="X26" s="35"/>
+      <c r="Y26" s="35"/>
+      <c r="Z26" s="35"/>
+      <c r="AA26" s="28"/>
+      <c r="AB26" s="28"/>
+      <c r="AC26" s="28"/>
+      <c r="AD26" s="29"/>
+      <c r="AE26" s="29"/>
+      <c r="AF26" s="29"/>
+      <c r="AG26" s="29"/>
+      <c r="AH26" s="29"/>
+      <c r="AI26" s="29"/>
+      <c r="AJ26" s="29"/>
+      <c r="AK26" s="29"/>
+      <c r="AL26" s="29"/>
+      <c r="AM26" s="29"/>
     </row>
-    <row r="27" spans="2:39" s="28" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="22"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="25"/>
-      <c r="L27" s="37"/>
-      <c r="O27" s="36"/>
-      <c r="P27" s="36"/>
-      <c r="Q27" s="36"/>
-      <c r="R27" s="36"/>
+    <row r="27" spans="2:39" s="27" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="21"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="36"/>
+      <c r="O27" s="35"/>
+      <c r="P27" s="35"/>
+      <c r="Q27" s="35"/>
+      <c r="R27" s="35"/>
       <c r="S27" s="5"/>
-      <c r="T27" s="36"/>
-      <c r="U27" s="36"/>
-      <c r="V27" s="36"/>
+      <c r="T27" s="35"/>
+      <c r="U27" s="35"/>
+      <c r="V27" s="35"/>
       <c r="W27" s="5"/>
-      <c r="X27" s="36"/>
-      <c r="Y27" s="36"/>
-      <c r="Z27" s="36"/>
-      <c r="AA27" s="29"/>
-      <c r="AB27" s="29"/>
-      <c r="AC27" s="29"/>
-      <c r="AD27" s="30"/>
-      <c r="AE27" s="30"/>
-      <c r="AF27" s="30"/>
-      <c r="AG27" s="30"/>
-      <c r="AH27" s="30"/>
-      <c r="AI27" s="30"/>
-      <c r="AJ27" s="30"/>
-      <c r="AK27" s="30"/>
-      <c r="AL27" s="30"/>
-      <c r="AM27" s="30"/>
+      <c r="X27" s="35"/>
+      <c r="Y27" s="35"/>
+      <c r="Z27" s="35"/>
+      <c r="AA27" s="28"/>
+      <c r="AB27" s="28"/>
+      <c r="AC27" s="28"/>
+      <c r="AD27" s="29"/>
+      <c r="AE27" s="29"/>
+      <c r="AF27" s="29"/>
+      <c r="AG27" s="29"/>
+      <c r="AH27" s="29"/>
+      <c r="AI27" s="29"/>
+      <c r="AJ27" s="29"/>
+      <c r="AK27" s="29"/>
+      <c r="AL27" s="29"/>
+      <c r="AM27" s="29"/>
     </row>
     <row r="28" spans="2:39" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B28" s="67" t="s">
+      <c r="B28" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="68"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="68"/>
-      <c r="F28" s="68"/>
-      <c r="G28" s="68"/>
-      <c r="H28" s="68"/>
-      <c r="I28" s="68"/>
-      <c r="J28" s="69"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="51"/>
+      <c r="J28" s="52"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
       <c r="O28" s="6"/>
       <c r="P28" s="6"/>
       <c r="Q28" s="6"/>
@@ -3569,32 +3573,32 @@
       <c r="AM28" s="4"/>
     </row>
     <row r="29" spans="2:39" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="67" t="s">
+      <c r="B29" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="68"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="68"/>
-      <c r="F29" s="68"/>
-      <c r="G29" s="68"/>
-      <c r="H29" s="68"/>
-      <c r="I29" s="68"/>
-      <c r="J29" s="69"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="9"/>
-      <c r="S29" s="7"/>
-      <c r="T29" s="9"/>
-      <c r="U29" s="9"/>
-      <c r="V29" s="9"/>
-      <c r="W29" s="3"/>
-      <c r="X29" s="6"/>
-      <c r="Y29" s="6"/>
-      <c r="Z29" s="6"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="69"/>
+      <c r="P29" s="69"/>
+      <c r="Q29" s="69"/>
+      <c r="R29" s="69"/>
+      <c r="S29" s="70"/>
+      <c r="T29" s="69"/>
+      <c r="U29" s="69"/>
+      <c r="V29" s="69"/>
+      <c r="W29" s="70"/>
+      <c r="X29" s="71"/>
+      <c r="Y29" s="71"/>
+      <c r="Z29" s="71"/>
       <c r="AA29" s="4"/>
       <c r="AB29" s="4"/>
       <c r="AC29" s="4"/>
@@ -3610,21 +3614,21 @@
       <c r="AM29" s="4"/>
     </row>
     <row r="30" spans="2:39" s="1" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="67" t="s">
+      <c r="B30" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="C30" s="68"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="68"/>
-      <c r="G30" s="68"/>
-      <c r="H30" s="68"/>
-      <c r="I30" s="68"/>
-      <c r="J30" s="69"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="12"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="11"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
@@ -3651,19 +3655,19 @@
       <c r="AM30" s="4"/>
     </row>
     <row r="31" spans="2:39" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="43" t="s">
+      <c r="B31" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="45"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="46"/>
-      <c r="F31" s="46"/>
-      <c r="G31" s="46"/>
-      <c r="H31" s="46"/>
-      <c r="I31" s="46"/>
-      <c r="J31" s="46"/>
-      <c r="K31" s="46"/>
-      <c r="L31" s="47"/>
+      <c r="C31" s="44"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="45"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="45"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="46"/>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
       <c r="Q31" s="2"/>
@@ -3691,52 +3695,25 @@
       <c r="AM31" s="4"/>
     </row>
     <row r="32" spans="2:39" x14ac:dyDescent="0.3">
-      <c r="B32" s="44"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="49"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="49"/>
-      <c r="L32" s="50"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="48"/>
+      <c r="I32" s="48"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="48"/>
+      <c r="L32" s="49"/>
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange password="C71F" sqref="O11:Z29" name="Aralık1_1"/>
+    <protectedRange password="C71F" sqref="O11:Z28" name="Aralık1_1"/>
+    <protectedRange password="C71F" sqref="O29:Z29" name="Aralık1_1_1"/>
   </protectedRanges>
   <mergeCells count="50">
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="B11:L11"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="B29:J29"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="B29:I29"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="X12:Z12"/>
@@ -3753,11 +3730,39 @@
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="C6:D6"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="G23:I23"/>
     <mergeCell ref="G22:I22"/>
     <mergeCell ref="G21:I21"/>
     <mergeCell ref="G20:I20"/>
     <mergeCell ref="G19:I19"/>
     <mergeCell ref="G18:I18"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="B11:L11"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="G13:I13"/>
   </mergeCells>
   <conditionalFormatting sqref="J12:K12 K16">
     <cfRule type="cellIs" dxfId="143" priority="247" operator="equal">
